--- a/manejo_reportes/SOL/ASIGNACIONES.xlsx
+++ b/manejo_reportes/SOL/ASIGNACIONES.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\report_download\manejo_reportes\SOL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0F25BD6-318A-45F4-9020-3AA6C60A2F2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D70B27C-CDBE-421A-8AA6-A50AFCF6B4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="11295" xr2:uid="{B1FF4C01-0A08-4889-A757-60BE544534DB}"/>
+    <workbookView xWindow="1305" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{B1FF4C01-0A08-4889-A757-60BE544534DB}"/>
   </bookViews>
   <sheets>
-    <sheet name="CONSOLIDADO_SOL_X_EVAL" sheetId="7" r:id="rId1"/>
+    <sheet name="CONSOLIDADO_SOL_X_EVAL" sheetId="8" r:id="rId1"/>
     <sheet name="IDENTIFICADOS" sheetId="1" r:id="rId2"/>
     <sheet name="REPORTADO_SIM" sheetId="2" r:id="rId3"/>
   </sheets>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="237">
   <si>
     <t>EXPEDIENTE</t>
   </si>
@@ -83,18 +83,9 @@
     <t>Hurtado Lago Briyan Deivi</t>
   </si>
   <si>
-    <t>LM240386704</t>
-  </si>
-  <si>
     <t>LM240386537</t>
   </si>
   <si>
-    <t>LM240386473</t>
-  </si>
-  <si>
-    <t>LM240386457</t>
-  </si>
-  <si>
     <t>LM240386069</t>
   </si>
   <si>
@@ -113,9 +104,6 @@
     <t>LM240385869</t>
   </si>
   <si>
-    <t>LM240385845</t>
-  </si>
-  <si>
     <t>LM240385623</t>
   </si>
   <si>
@@ -128,15 +116,6 @@
     <t>LM240385239</t>
   </si>
   <si>
-    <t>LM240384630</t>
-  </si>
-  <si>
-    <t>LM240384421</t>
-  </si>
-  <si>
-    <t>LM240383926</t>
-  </si>
-  <si>
     <t>LM240383874</t>
   </si>
   <si>
@@ -158,39 +137,15 @@
     <t>LM240381505</t>
   </si>
   <si>
-    <t>LM240381502</t>
-  </si>
-  <si>
     <t>LM240381205</t>
   </si>
   <si>
     <t>LM240380697</t>
   </si>
   <si>
-    <t>LM240380179</t>
-  </si>
-  <si>
-    <t>LM240380150</t>
-  </si>
-  <si>
-    <t>LM240380079</t>
-  </si>
-  <si>
-    <t>LM240379473</t>
-  </si>
-  <si>
-    <t>LM240379449</t>
-  </si>
-  <si>
     <t>LM240379448</t>
   </si>
   <si>
-    <t>LM240379429</t>
-  </si>
-  <si>
-    <t>LM240379405</t>
-  </si>
-  <si>
     <t>LM240379091</t>
   </si>
   <si>
@@ -212,9 +167,6 @@
     <t>LM240377422</t>
   </si>
   <si>
-    <t>LM240377281</t>
-  </si>
-  <si>
     <t>LM240375928</t>
   </si>
   <si>
@@ -248,36 +200,15 @@
     <t>LM240374599</t>
   </si>
   <si>
-    <t>LM240372115</t>
-  </si>
-  <si>
     <t>LM240372087</t>
   </si>
   <si>
     <t>LM240371714</t>
   </si>
   <si>
-    <t>LM240371580</t>
-  </si>
-  <si>
-    <t>LM240371549</t>
-  </si>
-  <si>
-    <t>LM240371409</t>
-  </si>
-  <si>
-    <t>LM240371397</t>
-  </si>
-  <si>
     <t>LM240371086</t>
   </si>
   <si>
-    <t>LM240369472</t>
-  </si>
-  <si>
-    <t>LM240368984</t>
-  </si>
-  <si>
     <t>LM240368874</t>
   </si>
   <si>
@@ -356,18 +287,12 @@
     <t>LM240361011</t>
   </si>
   <si>
-    <t>LM240360312</t>
-  </si>
-  <si>
     <t>LM240359910</t>
   </si>
   <si>
     <t>LM240359780</t>
   </si>
   <si>
-    <t>LM240359675</t>
-  </si>
-  <si>
     <t>LM240359217</t>
   </si>
   <si>
@@ -395,9 +320,6 @@
     <t>LM240346507</t>
   </si>
   <si>
-    <t>LM240342941</t>
-  </si>
-  <si>
     <t>LM240342718</t>
   </si>
   <si>
@@ -599,9 +521,6 @@
     <t>LM240391833</t>
   </si>
   <si>
-    <t>LM240391701</t>
-  </si>
-  <si>
     <t>LM240391644</t>
   </si>
   <si>
@@ -659,22 +578,175 @@
     <t>LM240388981</t>
   </si>
   <si>
-    <t>LM240388645</t>
-  </si>
-  <si>
-    <t>LM240388633</t>
-  </si>
-  <si>
-    <t>LM240388611</t>
-  </si>
-  <si>
-    <t>LM240388528</t>
-  </si>
-  <si>
     <t>LM240388501</t>
   </si>
   <si>
     <t>LM240388471</t>
+  </si>
+  <si>
+    <t>LM240395970</t>
+  </si>
+  <si>
+    <t>LM240395954</t>
+  </si>
+  <si>
+    <t>LM240395938</t>
+  </si>
+  <si>
+    <t>LM240395900</t>
+  </si>
+  <si>
+    <t>LM240395886</t>
+  </si>
+  <si>
+    <t>LM240395744</t>
+  </si>
+  <si>
+    <t>LM240395717</t>
+  </si>
+  <si>
+    <t>LM240395671</t>
+  </si>
+  <si>
+    <t>LM240395623</t>
+  </si>
+  <si>
+    <t>LM240395587</t>
+  </si>
+  <si>
+    <t>LM240395574</t>
+  </si>
+  <si>
+    <t>LM240395523</t>
+  </si>
+  <si>
+    <t>LM240395487</t>
+  </si>
+  <si>
+    <t>LM240395470</t>
+  </si>
+  <si>
+    <t>LM240395460</t>
+  </si>
+  <si>
+    <t>LM240395370</t>
+  </si>
+  <si>
+    <t>LM240395368</t>
+  </si>
+  <si>
+    <t>LM240395365</t>
+  </si>
+  <si>
+    <t>LM240395363</t>
+  </si>
+  <si>
+    <t>LM240395362</t>
+  </si>
+  <si>
+    <t>LM240395359</t>
+  </si>
+  <si>
+    <t>LM240395358</t>
+  </si>
+  <si>
+    <t>LM240395356</t>
+  </si>
+  <si>
+    <t>LM240395355</t>
+  </si>
+  <si>
+    <t>LM240395353</t>
+  </si>
+  <si>
+    <t>LM240395351</t>
+  </si>
+  <si>
+    <t>LM240395350</t>
+  </si>
+  <si>
+    <t>LM240395347</t>
+  </si>
+  <si>
+    <t>LM240395345</t>
+  </si>
+  <si>
+    <t>LM240395344</t>
+  </si>
+  <si>
+    <t>LM240395340</t>
+  </si>
+  <si>
+    <t>LM240395335</t>
+  </si>
+  <si>
+    <t>LM240395331</t>
+  </si>
+  <si>
+    <t>LM240395329</t>
+  </si>
+  <si>
+    <t>LM240395328</t>
+  </si>
+  <si>
+    <t>LM240395326</t>
+  </si>
+  <si>
+    <t>LM240395325</t>
+  </si>
+  <si>
+    <t>LM240395324</t>
+  </si>
+  <si>
+    <t>LM240395320</t>
+  </si>
+  <si>
+    <t>LM240395317</t>
+  </si>
+  <si>
+    <t>LM240395315</t>
+  </si>
+  <si>
+    <t>LM240395313</t>
+  </si>
+  <si>
+    <t>LM240395311</t>
+  </si>
+  <si>
+    <t>LM240395310</t>
+  </si>
+  <si>
+    <t>LM240395308</t>
+  </si>
+  <si>
+    <t>LM240395303</t>
+  </si>
+  <si>
+    <t>LM240395302</t>
+  </si>
+  <si>
+    <t>LM240395299</t>
+  </si>
+  <si>
+    <t>LM240395296</t>
+  </si>
+  <si>
+    <t>LM240395289</t>
+  </si>
+  <si>
+    <t>LM240394903</t>
+  </si>
+  <si>
+    <t>LM240394525</t>
+  </si>
+  <si>
+    <t>LM240394477</t>
+  </si>
+  <si>
+    <t>LM240393933</t>
+  </si>
+  <si>
+    <t>LM240393922</t>
   </si>
 </sst>
 </file>
@@ -1327,11 +1399,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{DDFA9DBE-3AC5-40BD-B573-DE54984C1937}" name="CONSOLIDADO_SOL_X_EVAL" displayName="CONSOLIDADO_SOL_X_EVAL" ref="A1:B204" totalsRowShown="0">
-  <autoFilter ref="A1:B204" xr:uid="{DDFA9DBE-3AC5-40BD-B573-DE54984C1937}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FB9CB89A-5533-42DB-A927-A5CE51F6D9CA}" name="CONSOLIDADO_SOL_X_EVAL" displayName="CONSOLIDADO_SOL_X_EVAL" ref="A1:B228" totalsRowShown="0">
+  <autoFilter ref="A1:B228" xr:uid="{FB9CB89A-5533-42DB-A927-A5CE51F6D9CA}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{7C55ECAD-0185-4C45-AA79-F08924C7CE76}" name="EXPEDIENTE"/>
-    <tableColumn id="2" xr3:uid="{2532ECFE-4F9D-45A0-9D30-6178542E35E1}" name="EVALUADOR"/>
+    <tableColumn id="1" xr3:uid="{141D3CE5-465C-4955-ACE8-430C57A8063C}" name="EXPEDIENTE"/>
+    <tableColumn id="2" xr3:uid="{BD3856EC-D3CC-4A45-BC47-F7A174C0E08B}" name="EVALUADOR"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1655,8 +1727,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{100A7A07-36E6-4939-8626-9C53B8DF4E2B}">
-  <dimension ref="A1:B204"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46DEB50F-ED05-44AB-93D6-2537E34F10DE}">
+  <dimension ref="A1:B228"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -1681,71 +1753,71 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="B3" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="B11" t="s">
         <v>4</v>
@@ -1753,439 +1825,439 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>157</v>
+        <v>191</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="B21" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>173</v>
+        <v>207</v>
       </c>
       <c r="B28" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="B29" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="B30" t="s">
-        <v>176</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="B31" t="s">
-        <v>176</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="B32" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="B33" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>180</v>
+        <v>213</v>
       </c>
       <c r="B34" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>181</v>
+        <v>214</v>
       </c>
       <c r="B35" t="s">
-        <v>176</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>182</v>
+        <v>215</v>
       </c>
       <c r="B36" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>183</v>
+        <v>216</v>
       </c>
       <c r="B37" t="s">
-        <v>176</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>184</v>
+        <v>217</v>
       </c>
       <c r="B38" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>185</v>
+        <v>218</v>
       </c>
       <c r="B39" t="s">
-        <v>176</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>186</v>
+        <v>219</v>
       </c>
       <c r="B40" t="s">
-        <v>176</v>
+        <v>28</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>187</v>
+        <v>220</v>
       </c>
       <c r="B41" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>188</v>
+        <v>221</v>
       </c>
       <c r="B42" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>189</v>
+        <v>222</v>
       </c>
       <c r="B43" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
       <c r="B44" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>191</v>
+        <v>224</v>
       </c>
       <c r="B45" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>192</v>
+        <v>225</v>
       </c>
       <c r="B46" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="B47" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>194</v>
+        <v>227</v>
       </c>
       <c r="B48" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="B49" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="B50" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="B51" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="B52" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>199</v>
+        <v>232</v>
       </c>
       <c r="B53" t="s">
-        <v>35</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>200</v>
+        <v>233</v>
       </c>
       <c r="B54" t="s">
-        <v>4</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>201</v>
+        <v>234</v>
       </c>
       <c r="B55" t="s">
-        <v>4</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="B56" t="s">
-        <v>4</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>203</v>
+        <v>236</v>
       </c>
       <c r="B57" t="s">
-        <v>4</v>
+        <v>150</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>204</v>
+        <v>122</v>
       </c>
       <c r="B58" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>205</v>
+        <v>123</v>
       </c>
       <c r="B59" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>206</v>
+        <v>124</v>
       </c>
       <c r="B60" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>207</v>
+        <v>125</v>
       </c>
       <c r="B61" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>208</v>
+        <v>126</v>
       </c>
       <c r="B62" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>209</v>
+        <v>127</v>
       </c>
       <c r="B63" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>210</v>
+        <v>128</v>
       </c>
       <c r="B64" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>211</v>
+        <v>129</v>
       </c>
       <c r="B65" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>212</v>
+        <v>130</v>
       </c>
       <c r="B66" t="s">
         <v>4</v>
@@ -2193,71 +2265,71 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>5</v>
+        <v>131</v>
       </c>
       <c r="B67" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>7</v>
+        <v>132</v>
       </c>
       <c r="B68" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="B69" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>9</v>
+        <v>134</v>
       </c>
       <c r="B70" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>10</v>
+        <v>135</v>
       </c>
       <c r="B71" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>11</v>
+        <v>136</v>
       </c>
       <c r="B72" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>12</v>
+        <v>137</v>
       </c>
       <c r="B73" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>13</v>
+        <v>138</v>
       </c>
       <c r="B74" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>15</v>
+        <v>139</v>
       </c>
       <c r="B75" t="s">
         <v>14</v>
@@ -2265,7 +2337,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="B76" t="s">
         <v>14</v>
@@ -2273,7 +2345,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="B77" t="s">
         <v>14</v>
@@ -2281,7 +2353,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>18</v>
+        <v>142</v>
       </c>
       <c r="B78" t="s">
         <v>14</v>
@@ -2289,7 +2361,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>19</v>
+        <v>143</v>
       </c>
       <c r="B79" t="s">
         <v>14</v>
@@ -2297,7 +2369,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="B80" t="s">
         <v>14</v>
@@ -2305,7 +2377,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="B81" t="s">
         <v>14</v>
@@ -2313,7 +2385,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>22</v>
+        <v>146</v>
       </c>
       <c r="B82" t="s">
         <v>14</v>
@@ -2321,7 +2393,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>23</v>
+        <v>147</v>
       </c>
       <c r="B83" t="s">
         <v>14</v>
@@ -2329,7 +2401,7 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>24</v>
+        <v>148</v>
       </c>
       <c r="B84" t="s">
         <v>14</v>
@@ -2337,23 +2409,23 @@
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>25</v>
+        <v>149</v>
       </c>
       <c r="B85" t="s">
-        <v>14</v>
+        <v>150</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>26</v>
+        <v>151</v>
       </c>
       <c r="B86" t="s">
-        <v>14</v>
+        <v>150</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>27</v>
+        <v>152</v>
       </c>
       <c r="B87" t="s">
         <v>14</v>
@@ -2361,7 +2433,7 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>28</v>
+        <v>153</v>
       </c>
       <c r="B88" t="s">
         <v>14</v>
@@ -2369,23 +2441,23 @@
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>29</v>
+        <v>154</v>
       </c>
       <c r="B89" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="B90" t="s">
-        <v>14</v>
+        <v>150</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c r="B91" t="s">
         <v>14</v>
@@ -2393,55 +2465,55 @@
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>32</v>
+        <v>157</v>
       </c>
       <c r="B92" t="s">
-        <v>14</v>
+        <v>150</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>33</v>
+        <v>158</v>
       </c>
       <c r="B93" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>36</v>
+        <v>159</v>
       </c>
       <c r="B94" t="s">
-        <v>34</v>
+        <v>150</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>37</v>
+        <v>160</v>
       </c>
       <c r="B95" t="s">
-        <v>34</v>
+        <v>150</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>38</v>
+        <v>161</v>
       </c>
       <c r="B96" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>39</v>
+        <v>162</v>
       </c>
       <c r="B97" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>40</v>
+        <v>163</v>
       </c>
       <c r="B98" t="s">
         <v>4</v>
@@ -2449,39 +2521,39 @@
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>41</v>
+        <v>164</v>
       </c>
       <c r="B99" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>42</v>
+        <v>165</v>
       </c>
       <c r="B100" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="B101" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>44</v>
+        <v>167</v>
       </c>
       <c r="B102" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="B103" t="s">
         <v>4</v>
@@ -2489,7 +2561,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>46</v>
+        <v>169</v>
       </c>
       <c r="B104" t="s">
         <v>4</v>
@@ -2497,7 +2569,7 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
       <c r="B105" t="s">
         <v>4</v>
@@ -2505,23 +2577,23 @@
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>48</v>
+        <v>171</v>
       </c>
       <c r="B106" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>49</v>
+        <v>172</v>
       </c>
       <c r="B107" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>50</v>
+        <v>173</v>
       </c>
       <c r="B108" t="s">
         <v>4</v>
@@ -2529,63 +2601,63 @@
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>51</v>
+        <v>174</v>
       </c>
       <c r="B109" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>52</v>
+        <v>175</v>
       </c>
       <c r="B110" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>53</v>
+        <v>176</v>
       </c>
       <c r="B111" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>54</v>
+        <v>177</v>
       </c>
       <c r="B112" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>55</v>
+        <v>178</v>
       </c>
       <c r="B113" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>56</v>
+        <v>179</v>
       </c>
       <c r="B114" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>57</v>
+        <v>180</v>
       </c>
       <c r="B115" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>58</v>
+        <v>181</v>
       </c>
       <c r="B116" t="s">
         <v>4</v>
@@ -2593,279 +2665,279 @@
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="B117" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="B118" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="B119" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="B120" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="B121" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="B122" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="B123" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="B124" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="B125" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="B126" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="B127" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="B128" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="B129" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="B130" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="B131" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="B132" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="B133" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="B134" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="B135" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="B136" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="B137" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="B138" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="B139" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="B140" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="B141" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="B142" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="B143" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="B144" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="B145" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="B146" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="B147" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="B148" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="B149" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="B150" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="B151" t="s">
         <v>6</v>
@@ -2873,7 +2945,7 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="B152" t="s">
         <v>6</v>
@@ -2881,7 +2953,7 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="B153" t="s">
         <v>6</v>
@@ -2889,7 +2961,7 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="B154" t="s">
         <v>6</v>
@@ -2897,7 +2969,7 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="B155" t="s">
         <v>6</v>
@@ -2905,7 +2977,7 @@
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="B156" t="s">
         <v>6</v>
@@ -2913,7 +2985,7 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="B157" t="s">
         <v>6</v>
@@ -2921,7 +2993,7 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="B158" t="s">
         <v>6</v>
@@ -2929,7 +3001,7 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="B159" t="s">
         <v>6</v>
@@ -2937,23 +3009,23 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="B160" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="B161" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="B162" t="s">
         <v>6</v>
@@ -2961,15 +3033,15 @@
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="B163" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="B164" t="s">
         <v>6</v>
@@ -2977,23 +3049,23 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="B165" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="B166" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="B167" t="s">
         <v>6</v>
@@ -3001,247 +3073,247 @@
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="B168" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="B169" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="B170" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="B171" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="B172" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="B173" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="B174" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="B175" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="B176" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="B177" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="B178" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>121</v>
+        <v>71</v>
       </c>
       <c r="B179" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="B180" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="B181" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="B182" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="B183" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="B184" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="B185" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="B186" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="B187" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="B188" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="B189" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="B190" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="B191" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>134</v>
+        <v>84</v>
       </c>
       <c r="B192" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="B193" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="B194" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>137</v>
+        <v>87</v>
       </c>
       <c r="B195" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>138</v>
+        <v>88</v>
       </c>
       <c r="B196" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="B197" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="B198" t="s">
         <v>4</v>
@@ -3249,7 +3321,7 @@
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>141</v>
+        <v>91</v>
       </c>
       <c r="B199" t="s">
         <v>4</v>
@@ -3257,15 +3329,15 @@
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>142</v>
+        <v>92</v>
       </c>
       <c r="B200" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>143</v>
+        <v>93</v>
       </c>
       <c r="B201" t="s">
         <v>4</v>
@@ -3273,26 +3345,218 @@
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>144</v>
+        <v>94</v>
       </c>
       <c r="B202" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>146</v>
+        <v>95</v>
       </c>
       <c r="B203" t="s">
-        <v>145</v>
+        <v>4</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>147</v>
+        <v>96</v>
       </c>
       <c r="B204" t="s">
-        <v>145</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>97</v>
+      </c>
+      <c r="B205" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>98</v>
+      </c>
+      <c r="B206" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>99</v>
+      </c>
+      <c r="B207" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>100</v>
+      </c>
+      <c r="B208" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>101</v>
+      </c>
+      <c r="B209" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>102</v>
+      </c>
+      <c r="B210" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>103</v>
+      </c>
+      <c r="B211" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>104</v>
+      </c>
+      <c r="B212" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>105</v>
+      </c>
+      <c r="B213" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>106</v>
+      </c>
+      <c r="B214" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>107</v>
+      </c>
+      <c r="B215" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>108</v>
+      </c>
+      <c r="B216" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>109</v>
+      </c>
+      <c r="B217" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>110</v>
+      </c>
+      <c r="B218" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>111</v>
+      </c>
+      <c r="B219" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>112</v>
+      </c>
+      <c r="B220" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>113</v>
+      </c>
+      <c r="B221" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>114</v>
+      </c>
+      <c r="B222" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>115</v>
+      </c>
+      <c r="B223" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>116</v>
+      </c>
+      <c r="B224" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>117</v>
+      </c>
+      <c r="B225" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>118</v>
+      </c>
+      <c r="B226" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>120</v>
+      </c>
+      <c r="B227" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>121</v>
+      </c>
+      <c r="B228" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -3338,7 +3602,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{418B94BA-4EB1-4C3C-A4AF-81071572DC18}">
-  <dimension ref="A1:B203"/>
+  <dimension ref="A1:B227"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -3355,71 +3619,71 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="B2" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>149</v>
+        <v>183</v>
       </c>
       <c r="B3" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>150</v>
+        <v>184</v>
       </c>
       <c r="B4" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>151</v>
+        <v>185</v>
       </c>
       <c r="B5" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>152</v>
+        <v>186</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>153</v>
+        <v>187</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>154</v>
+        <v>188</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>155</v>
+        <v>189</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>156</v>
+        <v>190</v>
       </c>
       <c r="B10" t="s">
         <v>4</v>
@@ -3427,439 +3691,439 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>157</v>
+        <v>191</v>
       </c>
       <c r="B11" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>158</v>
+        <v>192</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>159</v>
+        <v>193</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>160</v>
+        <v>194</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>161</v>
+        <v>195</v>
       </c>
       <c r="B15" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>162</v>
+        <v>196</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>163</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>164</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>165</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>167</v>
+        <v>201</v>
       </c>
       <c r="B21" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>168</v>
+        <v>202</v>
       </c>
       <c r="B22" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="B23" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>170</v>
+        <v>204</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="B25" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>172</v>
+        <v>206</v>
       </c>
       <c r="B26" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>173</v>
+        <v>207</v>
       </c>
       <c r="B27" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="B28" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>175</v>
+        <v>209</v>
       </c>
       <c r="B29" t="s">
-        <v>176</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>177</v>
+        <v>210</v>
       </c>
       <c r="B30" t="s">
-        <v>176</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="B31" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>179</v>
+        <v>212</v>
       </c>
       <c r="B32" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>180</v>
+        <v>213</v>
       </c>
       <c r="B33" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>181</v>
+        <v>214</v>
       </c>
       <c r="B34" t="s">
-        <v>176</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>182</v>
+        <v>215</v>
       </c>
       <c r="B35" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>183</v>
+        <v>216</v>
       </c>
       <c r="B36" t="s">
-        <v>176</v>
+        <v>28</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>184</v>
+        <v>217</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>185</v>
+        <v>218</v>
       </c>
       <c r="B38" t="s">
-        <v>176</v>
+        <v>28</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>186</v>
+        <v>219</v>
       </c>
       <c r="B39" t="s">
-        <v>176</v>
+        <v>28</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>187</v>
+        <v>220</v>
       </c>
       <c r="B40" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>188</v>
+        <v>221</v>
       </c>
       <c r="B41" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>189</v>
+        <v>222</v>
       </c>
       <c r="B42" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>190</v>
+        <v>223</v>
       </c>
       <c r="B43" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>191</v>
+        <v>224</v>
       </c>
       <c r="B44" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>192</v>
+        <v>225</v>
       </c>
       <c r="B45" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>193</v>
+        <v>226</v>
       </c>
       <c r="B46" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>194</v>
+        <v>227</v>
       </c>
       <c r="B47" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="B48" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>196</v>
+        <v>229</v>
       </c>
       <c r="B49" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>197</v>
+        <v>230</v>
       </c>
       <c r="B50" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>198</v>
+        <v>231</v>
       </c>
       <c r="B51" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>199</v>
+        <v>232</v>
       </c>
       <c r="B52" t="s">
-        <v>35</v>
+        <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>200</v>
+        <v>233</v>
       </c>
       <c r="B53" t="s">
-        <v>4</v>
+        <v>150</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>201</v>
+        <v>234</v>
       </c>
       <c r="B54" t="s">
-        <v>4</v>
+        <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>202</v>
+        <v>235</v>
       </c>
       <c r="B55" t="s">
-        <v>4</v>
+        <v>150</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>203</v>
+        <v>236</v>
       </c>
       <c r="B56" t="s">
-        <v>4</v>
+        <v>150</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>204</v>
+        <v>122</v>
       </c>
       <c r="B57" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>205</v>
+        <v>123</v>
       </c>
       <c r="B58" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>206</v>
+        <v>124</v>
       </c>
       <c r="B59" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>207</v>
+        <v>125</v>
       </c>
       <c r="B60" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>208</v>
+        <v>126</v>
       </c>
       <c r="B61" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>209</v>
+        <v>127</v>
       </c>
       <c r="B62" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>210</v>
+        <v>128</v>
       </c>
       <c r="B63" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>211</v>
+        <v>129</v>
       </c>
       <c r="B64" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>212</v>
+        <v>130</v>
       </c>
       <c r="B65" t="s">
         <v>4</v>
@@ -3867,71 +4131,71 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>5</v>
+        <v>131</v>
       </c>
       <c r="B66" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>7</v>
+        <v>132</v>
       </c>
       <c r="B67" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>8</v>
+        <v>133</v>
       </c>
       <c r="B68" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>9</v>
+        <v>134</v>
       </c>
       <c r="B69" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>10</v>
+        <v>135</v>
       </c>
       <c r="B70" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>11</v>
+        <v>136</v>
       </c>
       <c r="B71" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>12</v>
+        <v>137</v>
       </c>
       <c r="B72" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>13</v>
+        <v>138</v>
       </c>
       <c r="B73" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>15</v>
+        <v>139</v>
       </c>
       <c r="B74" t="s">
         <v>14</v>
@@ -3939,7 +4203,7 @@
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>16</v>
+        <v>140</v>
       </c>
       <c r="B75" t="s">
         <v>14</v>
@@ -3947,7 +4211,7 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>17</v>
+        <v>141</v>
       </c>
       <c r="B76" t="s">
         <v>14</v>
@@ -3955,7 +4219,7 @@
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>18</v>
+        <v>142</v>
       </c>
       <c r="B77" t="s">
         <v>14</v>
@@ -3963,7 +4227,7 @@
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>19</v>
+        <v>143</v>
       </c>
       <c r="B78" t="s">
         <v>14</v>
@@ -3971,7 +4235,7 @@
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="B79" t="s">
         <v>14</v>
@@ -3979,7 +4243,7 @@
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="B80" t="s">
         <v>14</v>
@@ -3987,7 +4251,7 @@
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>22</v>
+        <v>146</v>
       </c>
       <c r="B81" t="s">
         <v>14</v>
@@ -3995,7 +4259,7 @@
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>23</v>
+        <v>147</v>
       </c>
       <c r="B82" t="s">
         <v>14</v>
@@ -4003,7 +4267,7 @@
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>24</v>
+        <v>148</v>
       </c>
       <c r="B83" t="s">
         <v>14</v>
@@ -4011,23 +4275,23 @@
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>25</v>
+        <v>149</v>
       </c>
       <c r="B84" t="s">
-        <v>14</v>
+        <v>150</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>26</v>
+        <v>151</v>
       </c>
       <c r="B85" t="s">
-        <v>14</v>
+        <v>150</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>27</v>
+        <v>152</v>
       </c>
       <c r="B86" t="s">
         <v>14</v>
@@ -4035,7 +4299,7 @@
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>28</v>
+        <v>153</v>
       </c>
       <c r="B87" t="s">
         <v>14</v>
@@ -4043,23 +4307,23 @@
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>29</v>
+        <v>154</v>
       </c>
       <c r="B88" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>30</v>
+        <v>155</v>
       </c>
       <c r="B89" t="s">
-        <v>14</v>
+        <v>150</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>31</v>
+        <v>156</v>
       </c>
       <c r="B90" t="s">
         <v>14</v>
@@ -4067,55 +4331,55 @@
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>32</v>
+        <v>157</v>
       </c>
       <c r="B91" t="s">
-        <v>14</v>
+        <v>150</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>33</v>
+        <v>158</v>
       </c>
       <c r="B92" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>36</v>
+        <v>159</v>
       </c>
       <c r="B93" t="s">
-        <v>34</v>
+        <v>150</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>37</v>
+        <v>160</v>
       </c>
       <c r="B94" t="s">
-        <v>34</v>
+        <v>150</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>38</v>
+        <v>161</v>
       </c>
       <c r="B95" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>39</v>
+        <v>162</v>
       </c>
       <c r="B96" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>40</v>
+        <v>163</v>
       </c>
       <c r="B97" t="s">
         <v>4</v>
@@ -4123,39 +4387,39 @@
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>41</v>
+        <v>164</v>
       </c>
       <c r="B98" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>42</v>
+        <v>165</v>
       </c>
       <c r="B99" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>43</v>
+        <v>166</v>
       </c>
       <c r="B100" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>44</v>
+        <v>167</v>
       </c>
       <c r="B101" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>45</v>
+        <v>168</v>
       </c>
       <c r="B102" t="s">
         <v>4</v>
@@ -4163,7 +4427,7 @@
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>46</v>
+        <v>169</v>
       </c>
       <c r="B103" t="s">
         <v>4</v>
@@ -4171,7 +4435,7 @@
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>47</v>
+        <v>170</v>
       </c>
       <c r="B104" t="s">
         <v>4</v>
@@ -4179,23 +4443,23 @@
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>48</v>
+        <v>171</v>
       </c>
       <c r="B105" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>49</v>
+        <v>172</v>
       </c>
       <c r="B106" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>50</v>
+        <v>173</v>
       </c>
       <c r="B107" t="s">
         <v>4</v>
@@ -4203,63 +4467,63 @@
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>51</v>
+        <v>174</v>
       </c>
       <c r="B108" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>52</v>
+        <v>175</v>
       </c>
       <c r="B109" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>53</v>
+        <v>176</v>
       </c>
       <c r="B110" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>54</v>
+        <v>177</v>
       </c>
       <c r="B111" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>55</v>
+        <v>178</v>
       </c>
       <c r="B112" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>56</v>
+        <v>179</v>
       </c>
       <c r="B113" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>57</v>
+        <v>180</v>
       </c>
       <c r="B114" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>58</v>
+        <v>181</v>
       </c>
       <c r="B115" t="s">
         <v>4</v>
@@ -4267,279 +4531,279 @@
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>59</v>
+        <v>5</v>
       </c>
       <c r="B116" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>60</v>
+        <v>7</v>
       </c>
       <c r="B117" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="B118" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>62</v>
+        <v>9</v>
       </c>
       <c r="B119" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>63</v>
+        <v>10</v>
       </c>
       <c r="B120" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>64</v>
+        <v>11</v>
       </c>
       <c r="B121" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>65</v>
+        <v>12</v>
       </c>
       <c r="B122" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="B123" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="B124" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>68</v>
+        <v>16</v>
       </c>
       <c r="B125" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>69</v>
+        <v>17</v>
       </c>
       <c r="B126" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="B127" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="B128" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>72</v>
+        <v>20</v>
       </c>
       <c r="B129" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="B130" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>74</v>
+        <v>22</v>
       </c>
       <c r="B131" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>75</v>
+        <v>23</v>
       </c>
       <c r="B132" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>76</v>
+        <v>24</v>
       </c>
       <c r="B133" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>77</v>
+        <v>25</v>
       </c>
       <c r="B134" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="B135" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>79</v>
+        <v>29</v>
       </c>
       <c r="B136" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="B137" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="B138" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="B139" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="B140" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>84</v>
+        <v>34</v>
       </c>
       <c r="B141" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="B142" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="B143" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="B144" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>88</v>
+        <v>38</v>
       </c>
       <c r="B145" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="B146" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="B147" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>91</v>
+        <v>41</v>
       </c>
       <c r="B148" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>92</v>
+        <v>42</v>
       </c>
       <c r="B149" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>93</v>
+        <v>43</v>
       </c>
       <c r="B150" t="s">
         <v>6</v>
@@ -4547,7 +4811,7 @@
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>94</v>
+        <v>44</v>
       </c>
       <c r="B151" t="s">
         <v>6</v>
@@ -4555,7 +4819,7 @@
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="B152" t="s">
         <v>6</v>
@@ -4563,7 +4827,7 @@
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="B153" t="s">
         <v>6</v>
@@ -4571,7 +4835,7 @@
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>97</v>
+        <v>47</v>
       </c>
       <c r="B154" t="s">
         <v>6</v>
@@ -4579,7 +4843,7 @@
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="B155" t="s">
         <v>6</v>
@@ -4587,7 +4851,7 @@
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>99</v>
+        <v>49</v>
       </c>
       <c r="B156" t="s">
         <v>6</v>
@@ -4595,7 +4859,7 @@
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="B157" t="s">
         <v>6</v>
@@ -4603,7 +4867,7 @@
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="B158" t="s">
         <v>6</v>
@@ -4611,23 +4875,23 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="B159" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="B160" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>104</v>
+        <v>54</v>
       </c>
       <c r="B161" t="s">
         <v>6</v>
@@ -4635,15 +4899,15 @@
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="B162" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>106</v>
+        <v>56</v>
       </c>
       <c r="B163" t="s">
         <v>6</v>
@@ -4651,23 +4915,23 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>107</v>
+        <v>57</v>
       </c>
       <c r="B164" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>108</v>
+        <v>58</v>
       </c>
       <c r="B165" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="B166" t="s">
         <v>6</v>
@@ -4675,247 +4939,247 @@
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="B167" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>111</v>
+        <v>61</v>
       </c>
       <c r="B168" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="B169" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>113</v>
+        <v>63</v>
       </c>
       <c r="B170" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>114</v>
+        <v>64</v>
       </c>
       <c r="B171" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="B172" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="B173" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>117</v>
+        <v>67</v>
       </c>
       <c r="B174" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>118</v>
+        <v>68</v>
       </c>
       <c r="B175" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>119</v>
+        <v>69</v>
       </c>
       <c r="B176" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="B177" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>121</v>
+        <v>71</v>
       </c>
       <c r="B178" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="B179" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="B180" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="B181" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="B182" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>126</v>
+        <v>76</v>
       </c>
       <c r="B183" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>127</v>
+        <v>77</v>
       </c>
       <c r="B184" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="B185" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="B186" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>130</v>
+        <v>80</v>
       </c>
       <c r="B187" t="s">
-        <v>35</v>
+        <v>6</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>131</v>
+        <v>81</v>
       </c>
       <c r="B188" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>132</v>
+        <v>82</v>
       </c>
       <c r="B189" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>133</v>
+        <v>83</v>
       </c>
       <c r="B190" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>134</v>
+        <v>84</v>
       </c>
       <c r="B191" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="B192" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="B193" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>137</v>
+        <v>87</v>
       </c>
       <c r="B194" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>138</v>
+        <v>88</v>
       </c>
       <c r="B195" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>139</v>
+        <v>89</v>
       </c>
       <c r="B196" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>140</v>
+        <v>90</v>
       </c>
       <c r="B197" t="s">
         <v>4</v>
@@ -4923,7 +5187,7 @@
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>141</v>
+        <v>91</v>
       </c>
       <c r="B198" t="s">
         <v>4</v>
@@ -4931,15 +5195,15 @@
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>142</v>
+        <v>92</v>
       </c>
       <c r="B199" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>143</v>
+        <v>93</v>
       </c>
       <c r="B200" t="s">
         <v>4</v>
@@ -4947,26 +5211,218 @@
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>144</v>
+        <v>94</v>
       </c>
       <c r="B201" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>146</v>
+        <v>95</v>
       </c>
       <c r="B202" t="s">
-        <v>145</v>
+        <v>4</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>147</v>
+        <v>96</v>
       </c>
       <c r="B203" t="s">
-        <v>145</v>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>97</v>
+      </c>
+      <c r="B204" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>98</v>
+      </c>
+      <c r="B205" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>99</v>
+      </c>
+      <c r="B206" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>100</v>
+      </c>
+      <c r="B207" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>101</v>
+      </c>
+      <c r="B208" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>102</v>
+      </c>
+      <c r="B209" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>103</v>
+      </c>
+      <c r="B210" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>104</v>
+      </c>
+      <c r="B211" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>105</v>
+      </c>
+      <c r="B212" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>106</v>
+      </c>
+      <c r="B213" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>107</v>
+      </c>
+      <c r="B214" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>108</v>
+      </c>
+      <c r="B215" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>109</v>
+      </c>
+      <c r="B216" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>110</v>
+      </c>
+      <c r="B217" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>111</v>
+      </c>
+      <c r="B218" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>112</v>
+      </c>
+      <c r="B219" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>113</v>
+      </c>
+      <c r="B220" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>114</v>
+      </c>
+      <c r="B221" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>115</v>
+      </c>
+      <c r="B222" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>116</v>
+      </c>
+      <c r="B223" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>117</v>
+      </c>
+      <c r="B224" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>118</v>
+      </c>
+      <c r="B225" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>120</v>
+      </c>
+      <c r="B226" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>121</v>
+      </c>
+      <c r="B227" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/manejo_reportes/SOL/ASIGNACIONES.xlsx
+++ b/manejo_reportes/SOL/ASIGNACIONES.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\report_download\manejo_reportes\SOL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D70B27C-CDBE-421A-8AA6-A50AFCF6B4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{238DF471-A75A-45A0-95FC-E4994C9DB926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1305" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{B1FF4C01-0A08-4889-A757-60BE544534DB}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{B1FF4C01-0A08-4889-A757-60BE544534DB}"/>
   </bookViews>
   <sheets>
-    <sheet name="CONSOLIDADO_SOL_X_EVAL" sheetId="8" r:id="rId1"/>
+    <sheet name="CONSOLIDADO_SOL_X_EVAL" sheetId="9" r:id="rId1"/>
     <sheet name="IDENTIFICADOS" sheetId="1" r:id="rId2"/>
     <sheet name="REPORTADO_SIM" sheetId="2" r:id="rId3"/>
   </sheets>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="238">
   <si>
     <t>EXPEDIENTE</t>
   </si>
@@ -53,9 +53,6 @@
     <t>Loaiza Valdez, Raul</t>
   </si>
   <si>
-    <t>LM240388173</t>
-  </si>
-  <si>
     <t>Castillo Castillo Jose Marcello</t>
   </si>
   <si>
@@ -149,60 +146,21 @@
     <t>LM240379091</t>
   </si>
   <si>
-    <t>LM240378767</t>
-  </si>
-  <si>
     <t>LM240378020</t>
   </si>
   <si>
     <t>LM240378008</t>
   </si>
   <si>
-    <t>LM240377557</t>
-  </si>
-  <si>
-    <t>LM240377435</t>
-  </si>
-  <si>
-    <t>LM240377422</t>
-  </si>
-  <si>
-    <t>LM240375928</t>
-  </si>
-  <si>
     <t>LM240375919</t>
   </si>
   <si>
-    <t>LM240375918</t>
-  </si>
-  <si>
-    <t>LM240375910</t>
-  </si>
-  <si>
-    <t>LM240375909</t>
-  </si>
-  <si>
-    <t>LM240375894</t>
-  </si>
-  <si>
-    <t>LM240375893</t>
-  </si>
-  <si>
-    <t>LM240375837</t>
-  </si>
-  <si>
-    <t>LM240375836</t>
-  </si>
-  <si>
     <t>LM240374606</t>
   </si>
   <si>
     <t>LM240374599</t>
   </si>
   <si>
-    <t>LM240372087</t>
-  </si>
-  <si>
     <t>LM240371714</t>
   </si>
   <si>
@@ -296,12 +254,6 @@
     <t>LM240359217</t>
   </si>
   <si>
-    <t>LM240358227</t>
-  </si>
-  <si>
-    <t>LM240356010</t>
-  </si>
-  <si>
     <t>LM240355606</t>
   </si>
   <si>
@@ -377,9 +329,6 @@
     <t>LM240295841</t>
   </si>
   <si>
-    <t>LM240281596</t>
-  </si>
-  <si>
     <t>LM240272989</t>
   </si>
   <si>
@@ -428,9 +377,6 @@
     <t>LM240392365</t>
   </si>
   <si>
-    <t>LM240392272</t>
-  </si>
-  <si>
     <t>LM240392230</t>
   </si>
   <si>
@@ -491,9 +437,6 @@
     <t>Quispe Lopez, Aurora Esther Margarita</t>
   </si>
   <si>
-    <t>LM240391896</t>
-  </si>
-  <si>
     <t>LM240391892</t>
   </si>
   <si>
@@ -503,15 +446,9 @@
     <t>LM240391862</t>
   </si>
   <si>
-    <t>LM240391861</t>
-  </si>
-  <si>
     <t>LM240391860</t>
   </si>
   <si>
-    <t>LM240391848</t>
-  </si>
-  <si>
     <t>LM240391845</t>
   </si>
   <si>
@@ -530,18 +467,9 @@
     <t>LM240391335</t>
   </si>
   <si>
-    <t>LM240391317</t>
-  </si>
-  <si>
-    <t>LM240391295</t>
-  </si>
-  <si>
     <t>LM240391128</t>
   </si>
   <si>
-    <t>LM240391065</t>
-  </si>
-  <si>
     <t>LM240390853</t>
   </si>
   <si>
@@ -551,36 +479,15 @@
     <t>LM240390472</t>
   </si>
   <si>
-    <t>LM240390257</t>
-  </si>
-  <si>
-    <t>LM240390245</t>
-  </si>
-  <si>
-    <t>LM240390189</t>
-  </si>
-  <si>
-    <t>LM240390181</t>
-  </si>
-  <si>
-    <t>LM240390166</t>
-  </si>
-  <si>
     <t>LM240389928</t>
   </si>
   <si>
     <t>LM240389698</t>
   </si>
   <si>
-    <t>LM240389459</t>
-  </si>
-  <si>
     <t>LM240388981</t>
   </si>
   <si>
-    <t>LM240388501</t>
-  </si>
-  <si>
     <t>LM240388471</t>
   </si>
   <si>
@@ -747,6 +654,102 @@
   </si>
   <si>
     <t>LM240393922</t>
+  </si>
+  <si>
+    <t>LM240397364</t>
+  </si>
+  <si>
+    <t>LM240397352</t>
+  </si>
+  <si>
+    <t>LM240396851</t>
+  </si>
+  <si>
+    <t>LM240396823</t>
+  </si>
+  <si>
+    <t>LM240396527</t>
+  </si>
+  <si>
+    <t>LM240396503</t>
+  </si>
+  <si>
+    <t>LM240396483</t>
+  </si>
+  <si>
+    <t>LM240396474</t>
+  </si>
+  <si>
+    <t>LM240396440</t>
+  </si>
+  <si>
+    <t>LM240396295</t>
+  </si>
+  <si>
+    <t>LM240396281</t>
+  </si>
+  <si>
+    <t>LM240396244</t>
+  </si>
+  <si>
+    <t>LM240396185</t>
+  </si>
+  <si>
+    <t>LM240396182</t>
+  </si>
+  <si>
+    <t>LM240395293</t>
+  </si>
+  <si>
+    <t>LM240395292</t>
+  </si>
+  <si>
+    <t>LM240395239</t>
+  </si>
+  <si>
+    <t>LM240395137</t>
+  </si>
+  <si>
+    <t>LM240395051</t>
+  </si>
+  <si>
+    <t>LM240394953</t>
+  </si>
+  <si>
+    <t>LM240394937</t>
+  </si>
+  <si>
+    <t>LM240394893</t>
+  </si>
+  <si>
+    <t>LM240394858</t>
+  </si>
+  <si>
+    <t>LM240394790</t>
+  </si>
+  <si>
+    <t>Mejia Mercado Nathaly Lourdes</t>
+  </si>
+  <si>
+    <t>LM240394737</t>
+  </si>
+  <si>
+    <t>LM240394711</t>
+  </si>
+  <si>
+    <t>LM240394688</t>
+  </si>
+  <si>
+    <t>LM240394668</t>
+  </si>
+  <si>
+    <t>LM240394643</t>
+  </si>
+  <si>
+    <t>LM240394492</t>
+  </si>
+  <si>
+    <t>LM240394468</t>
   </si>
 </sst>
 </file>
@@ -1399,11 +1402,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FB9CB89A-5533-42DB-A927-A5CE51F6D9CA}" name="CONSOLIDADO_SOL_X_EVAL" displayName="CONSOLIDADO_SOL_X_EVAL" ref="A1:B228" totalsRowShown="0">
-  <autoFilter ref="A1:B228" xr:uid="{FB9CB89A-5533-42DB-A927-A5CE51F6D9CA}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{46F4DC77-49D3-4B12-B79E-9D146A2E039B}" name="CONSOLIDADO_SOL_X_EVAL" displayName="CONSOLIDADO_SOL_X_EVAL" ref="A1:B228" totalsRowShown="0">
+  <autoFilter ref="A1:B228" xr:uid="{46F4DC77-49D3-4B12-B79E-9D146A2E039B}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{141D3CE5-465C-4955-ACE8-430C57A8063C}" name="EXPEDIENTE"/>
-    <tableColumn id="2" xr3:uid="{BD3856EC-D3CC-4A45-BC47-F7A174C0E08B}" name="EVALUADOR"/>
+    <tableColumn id="1" xr3:uid="{032421E7-CB22-4ADB-AE67-AB0B06AD3F19}" name="EXPEDIENTE"/>
+    <tableColumn id="2" xr3:uid="{5D3CE035-9D08-46E6-9DBC-5BD220D4D80F}" name="EVALUADOR"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1727,7 +1730,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46DEB50F-ED05-44AB-93D6-2537E34F10DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{636BBB43-9AE7-480D-A368-1B7ADDA6C7E7}">
   <dimension ref="A1:B228"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -1753,927 +1756,927 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="B13" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="B14" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>196</v>
+        <v>151</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>198</v>
+        <v>153</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>201</v>
+        <v>156</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>202</v>
+        <v>157</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>203</v>
+        <v>158</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>204</v>
+        <v>159</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>205</v>
+        <v>160</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>207</v>
+        <v>162</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>208</v>
+        <v>163</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>209</v>
+        <v>164</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>210</v>
+        <v>165</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>211</v>
+        <v>166</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>212</v>
+        <v>167</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>213</v>
+        <v>168</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>214</v>
+        <v>169</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>215</v>
+        <v>170</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>217</v>
+        <v>172</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>218</v>
+        <v>173</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>219</v>
+        <v>174</v>
       </c>
       <c r="B40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>220</v>
+        <v>175</v>
       </c>
       <c r="B41" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>221</v>
+        <v>176</v>
       </c>
       <c r="B42" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>222</v>
+        <v>177</v>
       </c>
       <c r="B43" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>223</v>
+        <v>178</v>
       </c>
       <c r="B44" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>224</v>
+        <v>179</v>
       </c>
       <c r="B45" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>225</v>
+        <v>180</v>
       </c>
       <c r="B46" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>226</v>
+        <v>181</v>
       </c>
       <c r="B47" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>227</v>
+        <v>182</v>
       </c>
       <c r="B48" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>228</v>
+        <v>183</v>
       </c>
       <c r="B49" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>229</v>
+        <v>184</v>
       </c>
       <c r="B50" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>230</v>
+        <v>185</v>
       </c>
       <c r="B51" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>231</v>
+        <v>186</v>
       </c>
       <c r="B52" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>232</v>
+        <v>187</v>
       </c>
       <c r="B53" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="B54" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>234</v>
+        <v>189</v>
       </c>
       <c r="B55" t="s">
-        <v>150</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>235</v>
+        <v>190</v>
       </c>
       <c r="B56" t="s">
-        <v>150</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>236</v>
+        <v>191</v>
       </c>
       <c r="B57" t="s">
-        <v>150</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>122</v>
+        <v>192</v>
       </c>
       <c r="B58" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>123</v>
+        <v>193</v>
       </c>
       <c r="B59" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>124</v>
+        <v>194</v>
       </c>
       <c r="B60" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>125</v>
+        <v>195</v>
       </c>
       <c r="B61" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>126</v>
+        <v>196</v>
       </c>
       <c r="B62" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>127</v>
+        <v>197</v>
       </c>
       <c r="B63" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>128</v>
+        <v>198</v>
       </c>
       <c r="B64" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>129</v>
+        <v>199</v>
       </c>
       <c r="B65" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="B66" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>131</v>
+        <v>221</v>
       </c>
       <c r="B67" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>132</v>
+        <v>200</v>
       </c>
       <c r="B68" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>133</v>
+        <v>222</v>
       </c>
       <c r="B69" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>134</v>
+        <v>223</v>
       </c>
       <c r="B70" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>135</v>
+        <v>224</v>
       </c>
       <c r="B71" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>136</v>
+        <v>225</v>
       </c>
       <c r="B72" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>137</v>
+        <v>226</v>
       </c>
       <c r="B73" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>138</v>
+        <v>201</v>
       </c>
       <c r="B74" t="s">
-        <v>27</v>
+        <v>132</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>139</v>
+        <v>227</v>
       </c>
       <c r="B75" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>140</v>
+        <v>228</v>
       </c>
       <c r="B76" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>141</v>
+        <v>229</v>
       </c>
       <c r="B77" t="s">
-        <v>14</v>
+        <v>230</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>142</v>
+        <v>231</v>
       </c>
       <c r="B78" t="s">
-        <v>14</v>
+        <v>230</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>143</v>
+        <v>232</v>
       </c>
       <c r="B79" t="s">
-        <v>14</v>
+        <v>230</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>144</v>
+        <v>233</v>
       </c>
       <c r="B80" t="s">
-        <v>14</v>
+        <v>230</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>145</v>
+        <v>234</v>
       </c>
       <c r="B81" t="s">
-        <v>14</v>
+        <v>230</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>146</v>
+        <v>235</v>
       </c>
       <c r="B82" t="s">
-        <v>14</v>
+        <v>230</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>147</v>
+        <v>202</v>
       </c>
       <c r="B83" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>148</v>
+        <v>236</v>
       </c>
       <c r="B84" t="s">
-        <v>14</v>
+        <v>230</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="B85" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>151</v>
+        <v>237</v>
       </c>
       <c r="B86" t="s">
-        <v>150</v>
+        <v>230</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>152</v>
+        <v>204</v>
       </c>
       <c r="B87" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>153</v>
+        <v>205</v>
       </c>
       <c r="B88" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>154</v>
+        <v>105</v>
       </c>
       <c r="B89" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>155</v>
+        <v>106</v>
       </c>
       <c r="B90" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>156</v>
+        <v>107</v>
       </c>
       <c r="B91" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>157</v>
+        <v>108</v>
       </c>
       <c r="B92" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>158</v>
+        <v>109</v>
       </c>
       <c r="B93" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="B94" t="s">
-        <v>150</v>
+        <v>26</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="B95" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="B96" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>162</v>
+        <v>113</v>
       </c>
       <c r="B97" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>163</v>
+        <v>114</v>
       </c>
       <c r="B98" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>164</v>
+        <v>115</v>
       </c>
       <c r="B99" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
       <c r="B100" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>166</v>
+        <v>117</v>
       </c>
       <c r="B101" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>167</v>
+        <v>118</v>
       </c>
       <c r="B102" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>168</v>
+        <v>119</v>
       </c>
       <c r="B103" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="B104" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>170</v>
+        <v>121</v>
       </c>
       <c r="B105" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="B106" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>172</v>
+        <v>123</v>
       </c>
       <c r="B107" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>173</v>
+        <v>124</v>
       </c>
       <c r="B108" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>174</v>
+        <v>125</v>
       </c>
       <c r="B109" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>175</v>
+        <v>126</v>
       </c>
       <c r="B110" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="B111" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>177</v>
+        <v>128</v>
       </c>
       <c r="B112" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>178</v>
+        <v>129</v>
       </c>
       <c r="B113" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>179</v>
+        <v>130</v>
       </c>
       <c r="B114" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>180</v>
+        <v>131</v>
       </c>
       <c r="B115" t="s">
-        <v>28</v>
+        <v>132</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>181</v>
+        <v>133</v>
       </c>
       <c r="B116" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>5</v>
+        <v>134</v>
       </c>
       <c r="B117" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>7</v>
+        <v>135</v>
       </c>
       <c r="B118" t="s">
         <v>27</v>
@@ -2681,647 +2684,647 @@
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="B119" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>9</v>
+        <v>137</v>
       </c>
       <c r="B120" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="B121" t="s">
-        <v>4</v>
+        <v>132</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>11</v>
+        <v>139</v>
       </c>
       <c r="B122" t="s">
-        <v>4</v>
+        <v>132</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>12</v>
+        <v>140</v>
       </c>
       <c r="B123" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>13</v>
+        <v>141</v>
       </c>
       <c r="B124" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>15</v>
+        <v>142</v>
       </c>
       <c r="B125" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>16</v>
+        <v>143</v>
       </c>
       <c r="B126" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>17</v>
+        <v>144</v>
       </c>
       <c r="B127" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>18</v>
+        <v>145</v>
       </c>
       <c r="B128" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>19</v>
+        <v>146</v>
       </c>
       <c r="B129" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>20</v>
+        <v>147</v>
       </c>
       <c r="B130" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="B131" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>22</v>
+        <v>149</v>
       </c>
       <c r="B132" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>23</v>
+        <v>150</v>
       </c>
       <c r="B133" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B134" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B135" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B136" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B137" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B138" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B139" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B140" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B141" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="B142" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B143" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="B144" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B145" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="B146" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="B147" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="B148" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B149" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="B150" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="B151" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B152" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="B153" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B154" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B155" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B156" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B157" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B158" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="B159" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B160" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B161" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="B162" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B163" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B164" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B165" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="B166" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="B167" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="B168" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="B169" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B170" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="B171" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="B172" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="B173" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="B174" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="B175" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="B176" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="B177" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="B178" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="B179" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="B180" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="B181" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B182" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B183" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="B184" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="B185" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="B186" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B187" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="B188" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="B189" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="B190" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="B191" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="B192" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B193" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="B194" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="B195" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="B196" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="B197" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="B198" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="B199" t="s">
         <v>4</v>
@@ -3329,7 +3332,7 @@
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="B200" t="s">
         <v>4</v>
@@ -3337,7 +3340,7 @@
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="B201" t="s">
         <v>4</v>
@@ -3345,47 +3348,47 @@
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="B202" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="B203" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="B204" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="B205" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="B206" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B207" t="s">
         <v>4</v>
@@ -3393,7 +3396,7 @@
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="B208" t="s">
         <v>4</v>
@@ -3401,23 +3404,23 @@
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="B209" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="B210" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="B211" t="s">
         <v>4</v>
@@ -3425,23 +3428,23 @@
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="B212" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="B213" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="B214" t="s">
         <v>4</v>
@@ -3449,7 +3452,7 @@
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="B215" t="s">
         <v>4</v>
@@ -3457,7 +3460,7 @@
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="B216" t="s">
         <v>4</v>
@@ -3465,7 +3468,7 @@
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="B217" t="s">
         <v>4</v>
@@ -3473,7 +3476,7 @@
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="B218" t="s">
         <v>4</v>
@@ -3481,7 +3484,7 @@
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="B219" t="s">
         <v>4</v>
@@ -3489,7 +3492,7 @@
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="B220" t="s">
         <v>4</v>
@@ -3497,7 +3500,7 @@
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="B221" t="s">
         <v>4</v>
@@ -3505,7 +3508,7 @@
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="B222" t="s">
         <v>4</v>
@@ -3513,7 +3516,7 @@
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="B223" t="s">
         <v>4</v>
@@ -3521,15 +3524,15 @@
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="B224" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="B225" t="s">
         <v>4</v>
@@ -3537,7 +3540,7 @@
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="B226" t="s">
         <v>4</v>
@@ -3545,18 +3548,18 @@
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="B227" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="B228" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -3619,927 +3622,927 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>182</v>
+        <v>206</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>183</v>
+        <v>207</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="B5" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>187</v>
+        <v>211</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="B8" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>189</v>
+        <v>213</v>
       </c>
       <c r="B9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>190</v>
+        <v>214</v>
       </c>
       <c r="B10" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>191</v>
+        <v>215</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>192</v>
+        <v>216</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="B13" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="B15" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>196</v>
+        <v>151</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>198</v>
+        <v>153</v>
       </c>
       <c r="B18" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>199</v>
+        <v>154</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>200</v>
+        <v>155</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>201</v>
+        <v>156</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>202</v>
+        <v>157</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>203</v>
+        <v>158</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>204</v>
+        <v>159</v>
       </c>
       <c r="B24" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>205</v>
+        <v>160</v>
       </c>
       <c r="B25" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>206</v>
+        <v>161</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>207</v>
+        <v>162</v>
       </c>
       <c r="B27" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>208</v>
+        <v>163</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>209</v>
+        <v>164</v>
       </c>
       <c r="B29" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>210</v>
+        <v>165</v>
       </c>
       <c r="B30" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>211</v>
+        <v>166</v>
       </c>
       <c r="B31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>212</v>
+        <v>167</v>
       </c>
       <c r="B32" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>213</v>
+        <v>168</v>
       </c>
       <c r="B33" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>214</v>
+        <v>169</v>
       </c>
       <c r="B34" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>215</v>
+        <v>170</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>216</v>
+        <v>171</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>217</v>
+        <v>172</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>218</v>
+        <v>173</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>219</v>
+        <v>174</v>
       </c>
       <c r="B39" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>220</v>
+        <v>175</v>
       </c>
       <c r="B40" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>221</v>
+        <v>176</v>
       </c>
       <c r="B41" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>222</v>
+        <v>177</v>
       </c>
       <c r="B42" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>223</v>
+        <v>178</v>
       </c>
       <c r="B43" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>224</v>
+        <v>179</v>
       </c>
       <c r="B44" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>225</v>
+        <v>180</v>
       </c>
       <c r="B45" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>226</v>
+        <v>181</v>
       </c>
       <c r="B46" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>227</v>
+        <v>182</v>
       </c>
       <c r="B47" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>228</v>
+        <v>183</v>
       </c>
       <c r="B48" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>229</v>
+        <v>184</v>
       </c>
       <c r="B49" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>230</v>
+        <v>185</v>
       </c>
       <c r="B50" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>231</v>
+        <v>186</v>
       </c>
       <c r="B51" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>232</v>
+        <v>187</v>
       </c>
       <c r="B52" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>233</v>
+        <v>188</v>
       </c>
       <c r="B53" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>234</v>
+        <v>189</v>
       </c>
       <c r="B54" t="s">
-        <v>150</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>235</v>
+        <v>190</v>
       </c>
       <c r="B55" t="s">
-        <v>150</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>236</v>
+        <v>191</v>
       </c>
       <c r="B56" t="s">
-        <v>150</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>122</v>
+        <v>192</v>
       </c>
       <c r="B57" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>123</v>
+        <v>193</v>
       </c>
       <c r="B58" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>124</v>
+        <v>194</v>
       </c>
       <c r="B59" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>125</v>
+        <v>195</v>
       </c>
       <c r="B60" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>126</v>
+        <v>196</v>
       </c>
       <c r="B61" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>127</v>
+        <v>197</v>
       </c>
       <c r="B62" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>128</v>
+        <v>198</v>
       </c>
       <c r="B63" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>129</v>
+        <v>199</v>
       </c>
       <c r="B64" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>130</v>
+        <v>220</v>
       </c>
       <c r="B65" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>131</v>
+        <v>221</v>
       </c>
       <c r="B66" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>132</v>
+        <v>200</v>
       </c>
       <c r="B67" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>133</v>
+        <v>222</v>
       </c>
       <c r="B68" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>134</v>
+        <v>223</v>
       </c>
       <c r="B69" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>135</v>
+        <v>224</v>
       </c>
       <c r="B70" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>136</v>
+        <v>225</v>
       </c>
       <c r="B71" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>137</v>
+        <v>226</v>
       </c>
       <c r="B72" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>138</v>
+        <v>201</v>
       </c>
       <c r="B73" t="s">
-        <v>27</v>
+        <v>132</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>139</v>
+        <v>227</v>
       </c>
       <c r="B74" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>140</v>
+        <v>228</v>
       </c>
       <c r="B75" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>141</v>
+        <v>229</v>
       </c>
       <c r="B76" t="s">
-        <v>14</v>
+        <v>230</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>142</v>
+        <v>231</v>
       </c>
       <c r="B77" t="s">
-        <v>14</v>
+        <v>230</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>143</v>
+        <v>232</v>
       </c>
       <c r="B78" t="s">
-        <v>14</v>
+        <v>230</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>144</v>
+        <v>233</v>
       </c>
       <c r="B79" t="s">
-        <v>14</v>
+        <v>230</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>145</v>
+        <v>234</v>
       </c>
       <c r="B80" t="s">
-        <v>14</v>
+        <v>230</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>146</v>
+        <v>235</v>
       </c>
       <c r="B81" t="s">
-        <v>14</v>
+        <v>230</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>147</v>
+        <v>202</v>
       </c>
       <c r="B82" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>148</v>
+        <v>236</v>
       </c>
       <c r="B83" t="s">
-        <v>14</v>
+        <v>230</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="B84" t="s">
-        <v>150</v>
+        <v>132</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>151</v>
+        <v>237</v>
       </c>
       <c r="B85" t="s">
-        <v>150</v>
+        <v>230</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>152</v>
+        <v>204</v>
       </c>
       <c r="B86" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>153</v>
+        <v>205</v>
       </c>
       <c r="B87" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>154</v>
+        <v>105</v>
       </c>
       <c r="B88" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>155</v>
+        <v>106</v>
       </c>
       <c r="B89" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>156</v>
+        <v>107</v>
       </c>
       <c r="B90" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>157</v>
+        <v>108</v>
       </c>
       <c r="B91" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>158</v>
+        <v>109</v>
       </c>
       <c r="B92" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="B93" t="s">
-        <v>150</v>
+        <v>26</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="B94" t="s">
-        <v>150</v>
+        <v>27</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>161</v>
+        <v>112</v>
       </c>
       <c r="B95" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>162</v>
+        <v>113</v>
       </c>
       <c r="B96" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>163</v>
+        <v>114</v>
       </c>
       <c r="B97" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>164</v>
+        <v>115</v>
       </c>
       <c r="B98" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>165</v>
+        <v>116</v>
       </c>
       <c r="B99" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>166</v>
+        <v>117</v>
       </c>
       <c r="B100" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>167</v>
+        <v>118</v>
       </c>
       <c r="B101" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>168</v>
+        <v>119</v>
       </c>
       <c r="B102" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>169</v>
+        <v>120</v>
       </c>
       <c r="B103" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>170</v>
+        <v>121</v>
       </c>
       <c r="B104" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="B105" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>172</v>
+        <v>123</v>
       </c>
       <c r="B106" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>173</v>
+        <v>124</v>
       </c>
       <c r="B107" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>174</v>
+        <v>125</v>
       </c>
       <c r="B108" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>175</v>
+        <v>126</v>
       </c>
       <c r="B109" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>176</v>
+        <v>127</v>
       </c>
       <c r="B110" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>177</v>
+        <v>128</v>
       </c>
       <c r="B111" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>178</v>
+        <v>129</v>
       </c>
       <c r="B112" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>179</v>
+        <v>130</v>
       </c>
       <c r="B113" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>180</v>
+        <v>131</v>
       </c>
       <c r="B114" t="s">
-        <v>28</v>
+        <v>132</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>181</v>
+        <v>133</v>
       </c>
       <c r="B115" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>5</v>
+        <v>134</v>
       </c>
       <c r="B116" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>7</v>
+        <v>135</v>
       </c>
       <c r="B117" t="s">
         <v>27</v>
@@ -4547,647 +4550,647 @@
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>8</v>
+        <v>136</v>
       </c>
       <c r="B118" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>9</v>
+        <v>137</v>
       </c>
       <c r="B119" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="B120" t="s">
-        <v>4</v>
+        <v>132</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>11</v>
+        <v>139</v>
       </c>
       <c r="B121" t="s">
-        <v>4</v>
+        <v>132</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>12</v>
+        <v>140</v>
       </c>
       <c r="B122" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>13</v>
+        <v>141</v>
       </c>
       <c r="B123" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>15</v>
+        <v>142</v>
       </c>
       <c r="B124" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>16</v>
+        <v>143</v>
       </c>
       <c r="B125" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>17</v>
+        <v>144</v>
       </c>
       <c r="B126" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>18</v>
+        <v>145</v>
       </c>
       <c r="B127" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>19</v>
+        <v>146</v>
       </c>
       <c r="B128" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>20</v>
+        <v>147</v>
       </c>
       <c r="B129" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>21</v>
+        <v>148</v>
       </c>
       <c r="B130" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>22</v>
+        <v>149</v>
       </c>
       <c r="B131" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>23</v>
+        <v>150</v>
       </c>
       <c r="B132" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B133" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B134" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="B135" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B136" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="B137" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="B138" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B139" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="B140" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="B141" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="B142" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="B143" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B144" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="B145" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="B146" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="B147" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="B148" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="B149" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="B150" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="B151" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="B152" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B153" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B154" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="B155" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="B156" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B157" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="B158" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="B159" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="B160" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="B161" t="s">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="B162" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
       <c r="B163" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="B164" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>58</v>
+        <v>41</v>
       </c>
       <c r="B165" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="B166" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="B167" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="B168" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B169" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="B170" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="B171" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="B172" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="B173" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="B174" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="B175" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="B176" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="B177" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="B178" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="B179" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="B180" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B181" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>75</v>
+        <v>58</v>
       </c>
       <c r="B182" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
       <c r="B183" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="B184" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="B185" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="B186" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="B187" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="B188" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="B189" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="B190" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="B191" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>85</v>
+        <v>68</v>
       </c>
       <c r="B192" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="B193" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="B194" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="B195" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="B196" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="B197" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="B198" t="s">
         <v>4</v>
@@ -5195,7 +5198,7 @@
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="B199" t="s">
         <v>4</v>
@@ -5203,7 +5206,7 @@
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
       <c r="B200" t="s">
         <v>4</v>
@@ -5211,47 +5214,47 @@
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>94</v>
+        <v>77</v>
       </c>
       <c r="B201" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="B202" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="B203" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="B204" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="B205" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B206" t="s">
         <v>4</v>
@@ -5259,7 +5262,7 @@
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="B207" t="s">
         <v>4</v>
@@ -5267,23 +5270,23 @@
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="B208" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="B209" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="B210" t="s">
         <v>4</v>
@@ -5291,23 +5294,23 @@
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="B211" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>105</v>
+        <v>88</v>
       </c>
       <c r="B212" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>106</v>
+        <v>89</v>
       </c>
       <c r="B213" t="s">
         <v>4</v>
@@ -5315,7 +5318,7 @@
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="B214" t="s">
         <v>4</v>
@@ -5323,7 +5326,7 @@
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="B215" t="s">
         <v>4</v>
@@ -5331,7 +5334,7 @@
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="B216" t="s">
         <v>4</v>
@@ -5339,7 +5342,7 @@
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="B217" t="s">
         <v>4</v>
@@ -5347,7 +5350,7 @@
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
-        <v>111</v>
+        <v>94</v>
       </c>
       <c r="B218" t="s">
         <v>4</v>
@@ -5355,7 +5358,7 @@
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="B219" t="s">
         <v>4</v>
@@ -5363,7 +5366,7 @@
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="B220" t="s">
         <v>4</v>
@@ -5371,7 +5374,7 @@
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="B221" t="s">
         <v>4</v>
@@ -5379,7 +5382,7 @@
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="B222" t="s">
         <v>4</v>
@@ -5387,15 +5390,15 @@
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="B223" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="B224" t="s">
         <v>4</v>
@@ -5403,7 +5406,7 @@
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="B225" t="s">
         <v>4</v>
@@ -5411,18 +5414,18 @@
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="B226" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="B227" t="s">
-        <v>119</v>
+        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/manejo_reportes/SOL/ASIGNACIONES.xlsx
+++ b/manejo_reportes/SOL/ASIGNACIONES.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\report_download\manejo_reportes\SOL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{238DF471-A75A-45A0-95FC-E4994C9DB926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1406B44C-C6CA-462D-A52D-C4E90E81699D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{B1FF4C01-0A08-4889-A757-60BE544534DB}"/>
   </bookViews>
   <sheets>
-    <sheet name="CONSOLIDADO_SOL_X_EVAL" sheetId="9" r:id="rId1"/>
-    <sheet name="IDENTIFICADOS" sheetId="1" r:id="rId2"/>
-    <sheet name="REPORTADO_SIM" sheetId="2" r:id="rId3"/>
+    <sheet name="CONSOLIDADO_SOL_X_EVAL" sheetId="18" r:id="rId1"/>
+    <sheet name="Hoja1" sheetId="12" r:id="rId2"/>
+    <sheet name="IDENTIFICADOS" sheetId="1" r:id="rId3"/>
+    <sheet name="REPORTADO_SIM" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="238">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="710" uniqueCount="186">
   <si>
     <t>EXPEDIENTE</t>
   </si>
@@ -68,12 +69,6 @@
     <t>LM240387180</t>
   </si>
   <si>
-    <t>LM240386911</t>
-  </si>
-  <si>
-    <t>LM240386885</t>
-  </si>
-  <si>
     <t>LM240386807</t>
   </si>
   <si>
@@ -101,18 +96,9 @@
     <t>LM240385869</t>
   </si>
   <si>
-    <t>LM240385623</t>
-  </si>
-  <si>
-    <t>LM240385457</t>
-  </si>
-  <si>
     <t>LM240385412</t>
   </si>
   <si>
-    <t>LM240385239</t>
-  </si>
-  <si>
     <t>LM240383874</t>
   </si>
   <si>
@@ -128,18 +114,12 @@
     <t>LM240382595</t>
   </si>
   <si>
-    <t>LM240382392</t>
-  </si>
-  <si>
     <t>LM240381505</t>
   </si>
   <si>
     <t>LM240381205</t>
   </si>
   <si>
-    <t>LM240380697</t>
-  </si>
-  <si>
     <t>LM240379448</t>
   </si>
   <si>
@@ -173,12 +153,6 @@
     <t>LM240368739</t>
   </si>
   <si>
-    <t>LM240366468</t>
-  </si>
-  <si>
-    <t>LM240366446</t>
-  </si>
-  <si>
     <t>LM240366422</t>
   </si>
   <si>
@@ -188,18 +162,12 @@
     <t>LM240366396</t>
   </si>
   <si>
-    <t>LM240366367</t>
-  </si>
-  <si>
     <t>LM240366355</t>
   </si>
   <si>
     <t>LM240366329</t>
   </si>
   <si>
-    <t>LM240366296</t>
-  </si>
-  <si>
     <t>LM240366290</t>
   </si>
   <si>
@@ -212,39 +180,12 @@
     <t>LM240366240</t>
   </si>
   <si>
-    <t>LM240365985</t>
-  </si>
-  <si>
     <t>LM240365979</t>
   </si>
   <si>
-    <t>LM240365967</t>
-  </si>
-  <si>
-    <t>LM240365953</t>
-  </si>
-  <si>
-    <t>LM240365934</t>
-  </si>
-  <si>
-    <t>LM240365917</t>
-  </si>
-  <si>
-    <t>LM240365904</t>
-  </si>
-  <si>
-    <t>LM240365885</t>
-  </si>
-  <si>
-    <t>LM240365864</t>
-  </si>
-  <si>
     <t>LM240365349</t>
   </si>
   <si>
-    <t>LM240361011</t>
-  </si>
-  <si>
     <t>LM240359910</t>
   </si>
   <si>
@@ -266,9 +207,6 @@
     <t>LM240347630</t>
   </si>
   <si>
-    <t>LM240347123</t>
-  </si>
-  <si>
     <t>LM240346507</t>
   </si>
   <si>
@@ -281,15 +219,9 @@
     <t>LM240339264</t>
   </si>
   <si>
-    <t>LM240339204</t>
-  </si>
-  <si>
     <t>LM240334846</t>
   </si>
   <si>
-    <t>LM240334792</t>
-  </si>
-  <si>
     <t>LM240334427</t>
   </si>
   <si>
@@ -302,9 +234,6 @@
     <t>LM240312815</t>
   </si>
   <si>
-    <t>LM240309043</t>
-  </si>
-  <si>
     <t>LM240302177</t>
   </si>
   <si>
@@ -326,9 +255,6 @@
     <t>LM240300939</t>
   </si>
   <si>
-    <t>LM240295841</t>
-  </si>
-  <si>
     <t>LM240272989</t>
   </si>
   <si>
@@ -356,18 +282,9 @@
     <t>LM240393781</t>
   </si>
   <si>
-    <t>LM240393688</t>
-  </si>
-  <si>
     <t>LM240393313</t>
   </si>
   <si>
-    <t>LM240393272</t>
-  </si>
-  <si>
-    <t>LM240392490</t>
-  </si>
-  <si>
     <t>LM240392429</t>
   </si>
   <si>
@@ -386,69 +303,18 @@
     <t>LM240392200</t>
   </si>
   <si>
-    <t>LM240392190</t>
-  </si>
-  <si>
-    <t>LM240392178</t>
-  </si>
-  <si>
-    <t>LM240392156</t>
-  </si>
-  <si>
-    <t>LM240392144</t>
-  </si>
-  <si>
     <t>LM240392127</t>
   </si>
   <si>
-    <t>LM240392126</t>
-  </si>
-  <si>
-    <t>LM240392115</t>
-  </si>
-  <si>
-    <t>LM240392101</t>
-  </si>
-  <si>
-    <t>LM240392091</t>
-  </si>
-  <si>
-    <t>LM240392075</t>
-  </si>
-  <si>
-    <t>LM240392063</t>
-  </si>
-  <si>
-    <t>LM240392056</t>
-  </si>
-  <si>
     <t>LM240392043</t>
   </si>
   <si>
-    <t>LM240392028</t>
-  </si>
-  <si>
-    <t>LM240392012</t>
-  </si>
-  <si>
     <t>LM240391927</t>
   </si>
   <si>
-    <t>Quispe Lopez, Aurora Esther Margarita</t>
-  </si>
-  <si>
-    <t>LM240391892</t>
-  </si>
-  <si>
-    <t>LM240391879</t>
-  </si>
-  <si>
     <t>LM240391862</t>
   </si>
   <si>
-    <t>LM240391860</t>
-  </si>
-  <si>
     <t>LM240391845</t>
   </si>
   <si>
@@ -458,21 +324,12 @@
     <t>LM240391833</t>
   </si>
   <si>
-    <t>LM240391644</t>
-  </si>
-  <si>
     <t>LM240391638</t>
   </si>
   <si>
     <t>LM240391335</t>
   </si>
   <si>
-    <t>LM240391128</t>
-  </si>
-  <si>
-    <t>LM240390853</t>
-  </si>
-  <si>
     <t>LM240390664</t>
   </si>
   <si>
@@ -488,9 +345,6 @@
     <t>LM240388981</t>
   </si>
   <si>
-    <t>LM240388471</t>
-  </si>
-  <si>
     <t>LM240395970</t>
   </si>
   <si>
@@ -506,9 +360,6 @@
     <t>LM240395886</t>
   </si>
   <si>
-    <t>LM240395744</t>
-  </si>
-  <si>
     <t>LM240395717</t>
   </si>
   <si>
@@ -524,9 +375,6 @@
     <t>LM240395574</t>
   </si>
   <si>
-    <t>LM240395523</t>
-  </si>
-  <si>
     <t>LM240395487</t>
   </si>
   <si>
@@ -650,18 +498,6 @@
     <t>LM240394477</t>
   </si>
   <si>
-    <t>LM240393933</t>
-  </si>
-  <si>
-    <t>LM240393922</t>
-  </si>
-  <si>
-    <t>LM240397364</t>
-  </si>
-  <si>
-    <t>LM240397352</t>
-  </si>
-  <si>
     <t>LM240396851</t>
   </si>
   <si>
@@ -695,9 +531,6 @@
     <t>LM240396185</t>
   </si>
   <si>
-    <t>LM240396182</t>
-  </si>
-  <si>
     <t>LM240395293</t>
   </si>
   <si>
@@ -707,15 +540,9 @@
     <t>LM240395239</t>
   </si>
   <si>
-    <t>LM240395137</t>
-  </si>
-  <si>
     <t>LM240395051</t>
   </si>
   <si>
-    <t>LM240394953</t>
-  </si>
-  <si>
     <t>LM240394937</t>
   </si>
   <si>
@@ -734,22 +561,40 @@
     <t>LM240394737</t>
   </si>
   <si>
-    <t>LM240394711</t>
-  </si>
-  <si>
-    <t>LM240394688</t>
-  </si>
-  <si>
-    <t>LM240394668</t>
-  </si>
-  <si>
-    <t>LM240394643</t>
-  </si>
-  <si>
-    <t>LM240394492</t>
-  </si>
-  <si>
-    <t>LM240394468</t>
+    <t>LM240399414</t>
+  </si>
+  <si>
+    <t>LM240399312</t>
+  </si>
+  <si>
+    <t>LM240399283</t>
+  </si>
+  <si>
+    <t>LM240399246</t>
+  </si>
+  <si>
+    <t>LM240399202</t>
+  </si>
+  <si>
+    <t>LM240399120</t>
+  </si>
+  <si>
+    <t>LM240398146</t>
+  </si>
+  <si>
+    <t>LM240398130</t>
+  </si>
+  <si>
+    <t>LM240398030</t>
+  </si>
+  <si>
+    <t>LM240397810</t>
+  </si>
+  <si>
+    <t>LM240397792</t>
+  </si>
+  <si>
+    <t>LM240397471</t>
   </si>
 </sst>
 </file>
@@ -1402,11 +1247,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{46F4DC77-49D3-4B12-B79E-9D146A2E039B}" name="CONSOLIDADO_SOL_X_EVAL" displayName="CONSOLIDADO_SOL_X_EVAL" ref="A1:B228" totalsRowShown="0">
-  <autoFilter ref="A1:B228" xr:uid="{46F4DC77-49D3-4B12-B79E-9D146A2E039B}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FC163784-A7ED-4E68-897F-F5F7CF977101}" name="CONSOLIDADO_SOL_X_EVAL" displayName="CONSOLIDADO_SOL_X_EVAL" ref="A1:B177" totalsRowShown="0">
+  <autoFilter ref="A1:B177" xr:uid="{FC163784-A7ED-4E68-897F-F5F7CF977101}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{032421E7-CB22-4ADB-AE67-AB0B06AD3F19}" name="EXPEDIENTE"/>
-    <tableColumn id="2" xr3:uid="{5D3CE035-9D08-46E6-9DBC-5BD220D4D80F}" name="EVALUADOR"/>
+    <tableColumn id="1" xr3:uid="{DE0E4185-6FE5-4103-BB78-BA7FCCD3986B}" name="EXPEDIENTE"/>
+    <tableColumn id="2" xr3:uid="{3645CA1B-F503-4816-8BFB-FF98FDC66D52}" name="EVALUADOR"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1730,8 +1575,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{636BBB43-9AE7-480D-A368-1B7ADDA6C7E7}">
-  <dimension ref="A1:B228"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D59BAE-2641-4757-8252-1067969B7A63}">
+  <dimension ref="A1:B177"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -1756,191 +1601,191 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="B4" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="B6" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="B10" t="s">
-        <v>5</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>218</v>
+        <v>153</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>219</v>
+        <v>154</v>
       </c>
       <c r="B16" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B17" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B18" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B19" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B20" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B21" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B22" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B23" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B24" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B25" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>160</v>
+        <v>102</v>
       </c>
       <c r="B26" t="s">
         <v>4</v>
@@ -1948,7 +1793,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>161</v>
+        <v>103</v>
       </c>
       <c r="B27" t="s">
         <v>4</v>
@@ -1956,7 +1801,7 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>162</v>
+        <v>104</v>
       </c>
       <c r="B28" t="s">
         <v>4</v>
@@ -1964,271 +1809,271 @@
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>163</v>
+        <v>105</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>164</v>
+        <v>106</v>
       </c>
       <c r="B30" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="B31" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>166</v>
+        <v>108</v>
       </c>
       <c r="B32" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>167</v>
+        <v>109</v>
       </c>
       <c r="B33" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>168</v>
+        <v>110</v>
       </c>
       <c r="B34" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="B36" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="B37" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>172</v>
+        <v>114</v>
       </c>
       <c r="B38" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>173</v>
+        <v>115</v>
       </c>
       <c r="B39" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>174</v>
+        <v>116</v>
       </c>
       <c r="B40" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>175</v>
+        <v>117</v>
       </c>
       <c r="B41" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
       <c r="B42" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>177</v>
+        <v>119</v>
       </c>
       <c r="B43" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>178</v>
+        <v>120</v>
       </c>
       <c r="B44" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>179</v>
+        <v>121</v>
       </c>
       <c r="B45" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>180</v>
+        <v>122</v>
       </c>
       <c r="B46" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>181</v>
+        <v>123</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>182</v>
+        <v>124</v>
       </c>
       <c r="B48" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>183</v>
+        <v>125</v>
       </c>
       <c r="B49" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>184</v>
+        <v>126</v>
       </c>
       <c r="B50" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>185</v>
+        <v>127</v>
       </c>
       <c r="B51" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>186</v>
+        <v>128</v>
       </c>
       <c r="B52" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>187</v>
+        <v>129</v>
       </c>
       <c r="B53" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>188</v>
+        <v>130</v>
       </c>
       <c r="B54" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>189</v>
+        <v>131</v>
       </c>
       <c r="B55" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>190</v>
+        <v>132</v>
       </c>
       <c r="B56" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>191</v>
+        <v>133</v>
       </c>
       <c r="B57" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>192</v>
+        <v>134</v>
       </c>
       <c r="B58" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>193</v>
+        <v>135</v>
       </c>
       <c r="B59" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>194</v>
+        <v>136</v>
       </c>
       <c r="B60" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>195</v>
+        <v>137</v>
       </c>
       <c r="B61" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>196</v>
+        <v>138</v>
       </c>
       <c r="B62" t="s">
         <v>5</v>
@@ -2236,7 +2081,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>197</v>
+        <v>139</v>
       </c>
       <c r="B63" t="s">
         <v>5</v>
@@ -2244,7 +2089,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>198</v>
+        <v>140</v>
       </c>
       <c r="B64" t="s">
         <v>5</v>
@@ -2252,7 +2097,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>199</v>
+        <v>141</v>
       </c>
       <c r="B65" t="s">
         <v>5</v>
@@ -2260,7 +2105,7 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>220</v>
+        <v>142</v>
       </c>
       <c r="B66" t="s">
         <v>5</v>
@@ -2268,15 +2113,15 @@
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>221</v>
+        <v>143</v>
       </c>
       <c r="B67" t="s">
-        <v>132</v>
+        <v>5</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="B68" t="s">
         <v>5</v>
@@ -2284,15 +2129,15 @@
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>222</v>
+        <v>145</v>
       </c>
       <c r="B69" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>223</v>
+        <v>146</v>
       </c>
       <c r="B70" t="s">
         <v>5</v>
@@ -2300,487 +2145,487 @@
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>224</v>
+        <v>147</v>
       </c>
       <c r="B71" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>225</v>
+        <v>148</v>
       </c>
       <c r="B72" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>226</v>
+        <v>164</v>
       </c>
       <c r="B73" t="s">
-        <v>132</v>
+        <v>5</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="B74" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>227</v>
+        <v>149</v>
       </c>
       <c r="B75" t="s">
-        <v>132</v>
+        <v>5</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>228</v>
+        <v>166</v>
       </c>
       <c r="B76" t="s">
-        <v>132</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>229</v>
+        <v>167</v>
       </c>
       <c r="B77" t="s">
-        <v>230</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>231</v>
+        <v>168</v>
       </c>
       <c r="B78" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="B79" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>233</v>
+        <v>169</v>
       </c>
       <c r="B80" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>234</v>
+        <v>170</v>
       </c>
       <c r="B81" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>235</v>
+        <v>171</v>
       </c>
       <c r="B82" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>202</v>
+        <v>173</v>
       </c>
       <c r="B83" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>236</v>
+        <v>151</v>
       </c>
       <c r="B84" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>203</v>
+        <v>152</v>
       </c>
       <c r="B85" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>237</v>
+        <v>80</v>
       </c>
       <c r="B86" t="s">
-        <v>230</v>
+        <v>21</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>204</v>
+        <v>81</v>
       </c>
       <c r="B87" t="s">
-        <v>132</v>
+        <v>22</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="B88" t="s">
-        <v>132</v>
+        <v>21</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="B89" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="B90" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="B91" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="B92" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="B93" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="B94" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="B95" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B96" t="s">
-        <v>26</v>
+        <v>172</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="B97" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="B98" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="B99" t="s">
-        <v>13</v>
+        <v>172</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B100" t="s">
-        <v>13</v>
+        <v>172</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="B101" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="B102" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="B103" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="B104" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="B105" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="B106" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="B107" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>124</v>
+        <v>6</v>
       </c>
       <c r="B108" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>125</v>
+        <v>7</v>
       </c>
       <c r="B109" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>126</v>
+        <v>8</v>
       </c>
       <c r="B110" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>127</v>
+        <v>9</v>
       </c>
       <c r="B111" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>128</v>
+        <v>10</v>
       </c>
       <c r="B112" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>129</v>
+        <v>12</v>
       </c>
       <c r="B113" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>130</v>
+        <v>13</v>
       </c>
       <c r="B114" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>131</v>
+        <v>14</v>
       </c>
       <c r="B115" t="s">
-        <v>132</v>
+        <v>11</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>133</v>
+        <v>15</v>
       </c>
       <c r="B116" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>134</v>
+        <v>16</v>
       </c>
       <c r="B117" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>135</v>
+        <v>17</v>
       </c>
       <c r="B118" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>136</v>
+        <v>18</v>
       </c>
       <c r="B119" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="B120" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="B121" t="s">
-        <v>132</v>
+        <v>11</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>139</v>
+        <v>23</v>
       </c>
       <c r="B122" t="s">
-        <v>132</v>
+        <v>21</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>140</v>
+        <v>24</v>
       </c>
       <c r="B123" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="B124" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>142</v>
+        <v>26</v>
       </c>
       <c r="B125" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>143</v>
+        <v>27</v>
       </c>
       <c r="B126" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>144</v>
+        <v>28</v>
       </c>
       <c r="B127" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>145</v>
+        <v>29</v>
       </c>
       <c r="B128" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>146</v>
+        <v>30</v>
       </c>
       <c r="B129" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>147</v>
+        <v>31</v>
       </c>
       <c r="B130" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>148</v>
+        <v>32</v>
       </c>
       <c r="B131" t="s">
         <v>4</v>
@@ -2788,7 +2633,7 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>149</v>
+        <v>33</v>
       </c>
       <c r="B132" t="s">
         <v>4</v>
@@ -2796,31 +2641,31 @@
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>150</v>
+        <v>34</v>
       </c>
       <c r="B133" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="B134" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B135" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="B136" t="s">
         <v>4</v>
@@ -2828,183 +2673,183 @@
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="B137" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="B138" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B139" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="B140" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="B141" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="B142" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="B143" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="B144" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="B145" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="B146" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B147" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
+        <v>49</v>
+      </c>
+      <c r="B148" t="s">
         <v>21</v>
-      </c>
-      <c r="B148" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B149" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B150" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="B151" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="B152" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="B153" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="B154" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="B155" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="B156" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="B157" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="B158" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="B159" t="s">
         <v>4</v>
@@ -3012,39 +2857,39 @@
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="B160" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="B161" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="B162" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="B163" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="B164" t="s">
         <v>4</v>
@@ -3052,7 +2897,7 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="B165" t="s">
         <v>4</v>
@@ -3060,31 +2905,31 @@
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="B166" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="B167" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="B168" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B169" t="s">
         <v>4</v>
@@ -3092,31 +2937,31 @@
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="B170" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="B171" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="B172" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="B173" t="s">
         <v>5</v>
@@ -3124,442 +2969,34 @@
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="B174" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="B175" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="B176" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="B177" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
-        <v>53</v>
-      </c>
-      <c r="B178" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
-        <v>54</v>
-      </c>
-      <c r="B179" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
-        <v>55</v>
-      </c>
-      <c r="B180" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>56</v>
-      </c>
-      <c r="B181" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>57</v>
-      </c>
-      <c r="B182" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>58</v>
-      </c>
-      <c r="B183" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>59</v>
-      </c>
-      <c r="B184" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>60</v>
-      </c>
-      <c r="B185" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>61</v>
-      </c>
-      <c r="B186" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>62</v>
-      </c>
-      <c r="B187" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
-        <v>63</v>
-      </c>
-      <c r="B188" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>64</v>
-      </c>
-      <c r="B189" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>65</v>
-      </c>
-      <c r="B190" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
-        <v>66</v>
-      </c>
-      <c r="B191" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
-        <v>67</v>
-      </c>
-      <c r="B192" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
-        <v>68</v>
-      </c>
-      <c r="B193" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
-        <v>69</v>
-      </c>
-      <c r="B194" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>70</v>
-      </c>
-      <c r="B195" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>71</v>
-      </c>
-      <c r="B196" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>72</v>
-      </c>
-      <c r="B197" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>73</v>
-      </c>
-      <c r="B198" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>74</v>
-      </c>
-      <c r="B199" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>75</v>
-      </c>
-      <c r="B200" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>76</v>
-      </c>
-      <c r="B201" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
         <v>77</v>
-      </c>
-      <c r="B202" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
-        <v>78</v>
-      </c>
-      <c r="B203" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
-        <v>79</v>
-      </c>
-      <c r="B204" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
-        <v>80</v>
-      </c>
-      <c r="B205" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
-        <v>81</v>
-      </c>
-      <c r="B206" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
-        <v>82</v>
-      </c>
-      <c r="B207" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
-        <v>83</v>
-      </c>
-      <c r="B208" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
-        <v>84</v>
-      </c>
-      <c r="B209" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
-        <v>85</v>
-      </c>
-      <c r="B210" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
-        <v>86</v>
-      </c>
-      <c r="B211" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
-        <v>87</v>
-      </c>
-      <c r="B212" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
-        <v>88</v>
-      </c>
-      <c r="B213" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
-        <v>89</v>
-      </c>
-      <c r="B214" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
-        <v>90</v>
-      </c>
-      <c r="B215" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
-        <v>91</v>
-      </c>
-      <c r="B216" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>92</v>
-      </c>
-      <c r="B217" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
-        <v>93</v>
-      </c>
-      <c r="B218" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
-        <v>94</v>
-      </c>
-      <c r="B219" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
-        <v>95</v>
-      </c>
-      <c r="B220" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>96</v>
-      </c>
-      <c r="B221" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>97</v>
-      </c>
-      <c r="B222" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>98</v>
-      </c>
-      <c r="B223" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>99</v>
-      </c>
-      <c r="B224" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
-        <v>100</v>
-      </c>
-      <c r="B225" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
-        <v>101</v>
-      </c>
-      <c r="B226" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
-        <v>103</v>
-      </c>
-      <c r="B227" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
-        <v>104</v>
-      </c>
-      <c r="B228" t="s">
-        <v>102</v>
       </c>
     </row>
   </sheetData>
@@ -3571,6 +3008,15 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3059425-1448-4584-A7A0-84A3C8433016}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F93278DB-77B4-415B-B9F3-B81279C49AF1}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3603,9 +3049,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{418B94BA-4EB1-4C3C-A4AF-81071572DC18}">
-  <dimension ref="A1:B227"/>
+  <dimension ref="A1:B176"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
@@ -3622,191 +3068,191 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>208</v>
+        <v>176</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>210</v>
+        <v>178</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>212</v>
+        <v>180</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>213</v>
+        <v>181</v>
       </c>
       <c r="B9" t="s">
-        <v>5</v>
+        <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>214</v>
+        <v>182</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>215</v>
+        <v>183</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>216</v>
+        <v>184</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>172</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>217</v>
+        <v>185</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>218</v>
+        <v>153</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>219</v>
+        <v>154</v>
       </c>
       <c r="B15" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="B17" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B18" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B19" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B20" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B21" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B22" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B23" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B24" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>160</v>
+        <v>102</v>
       </c>
       <c r="B25" t="s">
         <v>4</v>
@@ -3814,7 +3260,7 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>161</v>
+        <v>103</v>
       </c>
       <c r="B26" t="s">
         <v>4</v>
@@ -3822,7 +3268,7 @@
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>162</v>
+        <v>104</v>
       </c>
       <c r="B27" t="s">
         <v>4</v>
@@ -3830,271 +3276,271 @@
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>163</v>
+        <v>105</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>164</v>
+        <v>106</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>165</v>
+        <v>107</v>
       </c>
       <c r="B30" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>166</v>
+        <v>108</v>
       </c>
       <c r="B31" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>167</v>
+        <v>109</v>
       </c>
       <c r="B32" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>168</v>
+        <v>110</v>
       </c>
       <c r="B33" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>169</v>
+        <v>111</v>
       </c>
       <c r="B34" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>170</v>
+        <v>112</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>171</v>
+        <v>113</v>
       </c>
       <c r="B36" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>172</v>
+        <v>114</v>
       </c>
       <c r="B37" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>173</v>
+        <v>115</v>
       </c>
       <c r="B38" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>174</v>
+        <v>116</v>
       </c>
       <c r="B39" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>175</v>
+        <v>117</v>
       </c>
       <c r="B40" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
       <c r="B41" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>177</v>
+        <v>119</v>
       </c>
       <c r="B42" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>178</v>
+        <v>120</v>
       </c>
       <c r="B43" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>179</v>
+        <v>121</v>
       </c>
       <c r="B44" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>180</v>
+        <v>122</v>
       </c>
       <c r="B45" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>181</v>
+        <v>123</v>
       </c>
       <c r="B46" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>182</v>
+        <v>124</v>
       </c>
       <c r="B47" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>183</v>
+        <v>125</v>
       </c>
       <c r="B48" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>184</v>
+        <v>126</v>
       </c>
       <c r="B49" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>185</v>
+        <v>127</v>
       </c>
       <c r="B50" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>186</v>
+        <v>128</v>
       </c>
       <c r="B51" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>187</v>
+        <v>129</v>
       </c>
       <c r="B52" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>188</v>
+        <v>130</v>
       </c>
       <c r="B53" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>189</v>
+        <v>131</v>
       </c>
       <c r="B54" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>190</v>
+        <v>132</v>
       </c>
       <c r="B55" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>191</v>
+        <v>133</v>
       </c>
       <c r="B56" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>192</v>
+        <v>134</v>
       </c>
       <c r="B57" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>193</v>
+        <v>135</v>
       </c>
       <c r="B58" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>194</v>
+        <v>136</v>
       </c>
       <c r="B59" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>195</v>
+        <v>137</v>
       </c>
       <c r="B60" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>196</v>
+        <v>138</v>
       </c>
       <c r="B61" t="s">
         <v>5</v>
@@ -4102,7 +3548,7 @@
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>197</v>
+        <v>139</v>
       </c>
       <c r="B62" t="s">
         <v>5</v>
@@ -4110,7 +3556,7 @@
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>198</v>
+        <v>140</v>
       </c>
       <c r="B63" t="s">
         <v>5</v>
@@ -4118,7 +3564,7 @@
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>199</v>
+        <v>141</v>
       </c>
       <c r="B64" t="s">
         <v>5</v>
@@ -4126,7 +3572,7 @@
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>220</v>
+        <v>142</v>
       </c>
       <c r="B65" t="s">
         <v>5</v>
@@ -4134,15 +3580,15 @@
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>221</v>
+        <v>143</v>
       </c>
       <c r="B66" t="s">
-        <v>132</v>
+        <v>5</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="B67" t="s">
         <v>5</v>
@@ -4150,15 +3596,15 @@
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>222</v>
+        <v>145</v>
       </c>
       <c r="B68" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>223</v>
+        <v>146</v>
       </c>
       <c r="B69" t="s">
         <v>5</v>
@@ -4166,487 +3612,487 @@
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>224</v>
+        <v>147</v>
       </c>
       <c r="B70" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>225</v>
+        <v>148</v>
       </c>
       <c r="B71" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>226</v>
+        <v>164</v>
       </c>
       <c r="B72" t="s">
-        <v>132</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>201</v>
+        <v>165</v>
       </c>
       <c r="B73" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>227</v>
+        <v>149</v>
       </c>
       <c r="B74" t="s">
-        <v>132</v>
+        <v>5</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>228</v>
+        <v>166</v>
       </c>
       <c r="B75" t="s">
-        <v>132</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>229</v>
+        <v>167</v>
       </c>
       <c r="B76" t="s">
-        <v>230</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>231</v>
+        <v>168</v>
       </c>
       <c r="B77" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>232</v>
+        <v>150</v>
       </c>
       <c r="B78" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>233</v>
+        <v>169</v>
       </c>
       <c r="B79" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>234</v>
+        <v>170</v>
       </c>
       <c r="B80" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>235</v>
+        <v>171</v>
       </c>
       <c r="B81" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>202</v>
+        <v>173</v>
       </c>
       <c r="B82" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>236</v>
+        <v>151</v>
       </c>
       <c r="B83" t="s">
-        <v>230</v>
+        <v>172</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>203</v>
+        <v>152</v>
       </c>
       <c r="B84" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>237</v>
+        <v>80</v>
       </c>
       <c r="B85" t="s">
-        <v>230</v>
+        <v>21</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>204</v>
+        <v>81</v>
       </c>
       <c r="B86" t="s">
-        <v>132</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="B87" t="s">
-        <v>132</v>
+        <v>21</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="B88" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="B89" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="B90" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>108</v>
+        <v>86</v>
       </c>
       <c r="B91" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>109</v>
+        <v>87</v>
       </c>
       <c r="B92" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>110</v>
+        <v>88</v>
       </c>
       <c r="B93" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="B94" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>112</v>
+        <v>90</v>
       </c>
       <c r="B95" t="s">
-        <v>26</v>
+        <v>172</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>113</v>
+        <v>91</v>
       </c>
       <c r="B96" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>114</v>
+        <v>92</v>
       </c>
       <c r="B97" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="B98" t="s">
-        <v>13</v>
+        <v>172</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B99" t="s">
-        <v>13</v>
+        <v>172</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="B100" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="B101" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="B102" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="B103" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="B104" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="B105" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="B106" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>124</v>
+        <v>6</v>
       </c>
       <c r="B107" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>125</v>
+        <v>7</v>
       </c>
       <c r="B108" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>126</v>
+        <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>127</v>
+        <v>9</v>
       </c>
       <c r="B110" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>128</v>
+        <v>10</v>
       </c>
       <c r="B111" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>129</v>
+        <v>12</v>
       </c>
       <c r="B112" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>130</v>
+        <v>13</v>
       </c>
       <c r="B113" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>131</v>
+        <v>14</v>
       </c>
       <c r="B114" t="s">
-        <v>132</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>133</v>
+        <v>15</v>
       </c>
       <c r="B115" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>134</v>
+        <v>16</v>
       </c>
       <c r="B116" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>135</v>
+        <v>17</v>
       </c>
       <c r="B117" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>136</v>
+        <v>18</v>
       </c>
       <c r="B118" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="B119" t="s">
-        <v>27</v>
+        <v>11</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="B120" t="s">
-        <v>132</v>
+        <v>11</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>139</v>
+        <v>23</v>
       </c>
       <c r="B121" t="s">
-        <v>132</v>
+        <v>21</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>140</v>
+        <v>24</v>
       </c>
       <c r="B122" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>141</v>
+        <v>25</v>
       </c>
       <c r="B123" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>142</v>
+        <v>26</v>
       </c>
       <c r="B124" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>143</v>
+        <v>27</v>
       </c>
       <c r="B125" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>144</v>
+        <v>28</v>
       </c>
       <c r="B126" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>145</v>
+        <v>29</v>
       </c>
       <c r="B127" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>146</v>
+        <v>30</v>
       </c>
       <c r="B128" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>147</v>
+        <v>31</v>
       </c>
       <c r="B129" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>148</v>
+        <v>32</v>
       </c>
       <c r="B130" t="s">
         <v>4</v>
@@ -4654,7 +4100,7 @@
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>149</v>
+        <v>33</v>
       </c>
       <c r="B131" t="s">
         <v>4</v>
@@ -4662,31 +4108,31 @@
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>150</v>
+        <v>34</v>
       </c>
       <c r="B132" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="B133" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B134" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>8</v>
+        <v>37</v>
       </c>
       <c r="B135" t="s">
         <v>4</v>
@@ -4694,183 +4140,183 @@
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="B136" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="B137" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B138" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="B139" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="B140" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="B141" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="B142" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="B143" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="B144" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="B145" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="B146" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>49</v>
+      </c>
+      <c r="B147" t="s">
         <v>21</v>
-      </c>
-      <c r="B147" t="s">
-        <v>13</v>
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="B148" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="B149" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="B150" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="B151" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="B152" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>29</v>
+        <v>55</v>
       </c>
       <c r="B153" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="B154" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="B155" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="B156" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="B157" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>34</v>
+        <v>60</v>
       </c>
       <c r="B158" t="s">
         <v>4</v>
@@ -4878,39 +4324,39 @@
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="B159" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="B160" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="B161" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="B162" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="B163" t="s">
         <v>4</v>
@@ -4918,7 +4364,7 @@
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="B164" t="s">
         <v>4</v>
@@ -4926,31 +4372,31 @@
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="B165" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>42</v>
+        <v>68</v>
       </c>
       <c r="B166" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="B167" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="B168" t="s">
         <v>4</v>
@@ -4958,31 +4404,31 @@
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="B169" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="B170" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="B171" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="B172" t="s">
         <v>5</v>
@@ -4990,442 +4436,34 @@
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="B173" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="B174" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="B175" t="s">
-        <v>5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="B176" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
-        <v>53</v>
-      </c>
-      <c r="B177" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A178" t="s">
-        <v>54</v>
-      </c>
-      <c r="B178" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A179" t="s">
-        <v>55</v>
-      </c>
-      <c r="B179" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A180" t="s">
-        <v>56</v>
-      </c>
-      <c r="B180" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>57</v>
-      </c>
-      <c r="B181" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A182" t="s">
-        <v>58</v>
-      </c>
-      <c r="B182" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A183" t="s">
-        <v>59</v>
-      </c>
-      <c r="B183" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
-        <v>60</v>
-      </c>
-      <c r="B184" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A185" t="s">
-        <v>61</v>
-      </c>
-      <c r="B185" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A186" t="s">
-        <v>62</v>
-      </c>
-      <c r="B186" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A187" t="s">
-        <v>63</v>
-      </c>
-      <c r="B187" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A188" t="s">
-        <v>64</v>
-      </c>
-      <c r="B188" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A189" t="s">
-        <v>65</v>
-      </c>
-      <c r="B189" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>66</v>
-      </c>
-      <c r="B190" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
-        <v>67</v>
-      </c>
-      <c r="B191" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A192" t="s">
-        <v>68</v>
-      </c>
-      <c r="B192" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A193" t="s">
-        <v>69</v>
-      </c>
-      <c r="B193" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A194" t="s">
-        <v>70</v>
-      </c>
-      <c r="B194" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>71</v>
-      </c>
-      <c r="B195" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A196" t="s">
-        <v>72</v>
-      </c>
-      <c r="B196" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A197" t="s">
-        <v>73</v>
-      </c>
-      <c r="B197" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A198" t="s">
-        <v>74</v>
-      </c>
-      <c r="B198" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A199" t="s">
-        <v>75</v>
-      </c>
-      <c r="B199" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A200" t="s">
-        <v>76</v>
-      </c>
-      <c r="B200" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
         <v>77</v>
-      </c>
-      <c r="B201" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A202" t="s">
-        <v>78</v>
-      </c>
-      <c r="B202" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A203" t="s">
-        <v>79</v>
-      </c>
-      <c r="B203" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A204" t="s">
-        <v>80</v>
-      </c>
-      <c r="B204" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A205" t="s">
-        <v>81</v>
-      </c>
-      <c r="B205" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
-        <v>82</v>
-      </c>
-      <c r="B206" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
-        <v>83</v>
-      </c>
-      <c r="B207" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
-        <v>84</v>
-      </c>
-      <c r="B208" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A209" t="s">
-        <v>85</v>
-      </c>
-      <c r="B209" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A210" t="s">
-        <v>86</v>
-      </c>
-      <c r="B210" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A211" t="s">
-        <v>87</v>
-      </c>
-      <c r="B211" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A212" t="s">
-        <v>88</v>
-      </c>
-      <c r="B212" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A213" t="s">
-        <v>89</v>
-      </c>
-      <c r="B213" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A214" t="s">
-        <v>90</v>
-      </c>
-      <c r="B214" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A215" t="s">
-        <v>91</v>
-      </c>
-      <c r="B215" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
-        <v>92</v>
-      </c>
-      <c r="B216" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>93</v>
-      </c>
-      <c r="B217" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
-        <v>94</v>
-      </c>
-      <c r="B218" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
-        <v>95</v>
-      </c>
-      <c r="B219" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
-        <v>96</v>
-      </c>
-      <c r="B220" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>97</v>
-      </c>
-      <c r="B221" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>98</v>
-      </c>
-      <c r="B222" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>99</v>
-      </c>
-      <c r="B223" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>100</v>
-      </c>
-      <c r="B224" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
-        <v>101</v>
-      </c>
-      <c r="B225" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
-        <v>103</v>
-      </c>
-      <c r="B226" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
-        <v>104</v>
-      </c>
-      <c r="B227" t="s">
-        <v>102</v>
       </c>
     </row>
   </sheetData>

--- a/manejo_reportes/SOL/ASIGNACIONES.xlsx
+++ b/manejo_reportes/SOL/ASIGNACIONES.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\report_download\manejo_reportes\SOL\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1406B44C-C6CA-462D-A52D-C4E90E81699D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96DE7C83-2569-447A-9534-CA6656006857}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="11295" xr2:uid="{B1FF4C01-0A08-4889-A757-60BE544534DB}"/>
   </bookViews>
   <sheets>
-    <sheet name="CONSOLIDADO_SOL_X_EVAL" sheetId="18" r:id="rId1"/>
+    <sheet name="CONSOLIDADO_SOL_X_EVAL" sheetId="19" r:id="rId1"/>
     <sheet name="Hoja1" sheetId="12" r:id="rId2"/>
     <sheet name="IDENTIFICADOS" sheetId="1" r:id="rId3"/>
     <sheet name="REPORTADO_SIM" sheetId="2" r:id="rId4"/>
@@ -1247,11 +1247,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{FC163784-A7ED-4E68-897F-F5F7CF977101}" name="CONSOLIDADO_SOL_X_EVAL" displayName="CONSOLIDADO_SOL_X_EVAL" ref="A1:B177" totalsRowShown="0">
-  <autoFilter ref="A1:B177" xr:uid="{FC163784-A7ED-4E68-897F-F5F7CF977101}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{8E233776-F8AF-4976-A615-17717602F036}" name="CONSOLIDADO_SOL_X_EVAL" displayName="CONSOLIDADO_SOL_X_EVAL" ref="A1:B177" totalsRowShown="0">
+  <autoFilter ref="A1:B177" xr:uid="{8E233776-F8AF-4976-A615-17717602F036}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{DE0E4185-6FE5-4103-BB78-BA7FCCD3986B}" name="EXPEDIENTE"/>
-    <tableColumn id="2" xr3:uid="{3645CA1B-F503-4816-8BFB-FF98FDC66D52}" name="EVALUADOR"/>
+    <tableColumn id="1" xr3:uid="{42715B62-A205-44DA-9C9A-6459310E56A9}" name="EXPEDIENTE"/>
+    <tableColumn id="2" xr3:uid="{EA34C329-420C-46C6-8F55-26C4C7F26E15}" name="EVALUADOR"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1575,7 +1575,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D59BAE-2641-4757-8252-1067969B7A63}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{428054C8-22FA-4AFF-B3D8-1BCA4EB98D88}">
   <dimension ref="A1:B177"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
